--- a/list of gates updated.xlsx
+++ b/list of gates updated.xlsx
@@ -7270,10 +7270,10 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1" t="s">
+      <c r="A137" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B137" s="2" t="n">
+      <c r="B137" s="8" t="n">
         <v>46</v>
       </c>
       <c r="C137" s="23" t="str">
@@ -7534,10 +7534,10 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="1" t="s">
+      <c r="A152" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B152" s="2" t="n">
+      <c r="B152" s="8" t="n">
         <v>62</v>
       </c>
       <c r="C152" s="24" t="str">
@@ -7552,10 +7552,10 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
+      <c r="A153" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B153" s="2" t="n">
+      <c r="B153" s="8" t="n">
         <v>63</v>
       </c>
       <c r="C153" s="24" t="str">
@@ -7570,10 +7570,10 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B154" s="2" t="n">
+      <c r="B154" s="8" t="n">
         <v>64</v>
       </c>
       <c r="C154" s="24" t="str">
@@ -7588,10 +7588,10 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="1" t="s">
+      <c r="A155" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B155" s="2" t="n">
+      <c r="B155" s="8" t="n">
         <v>65</v>
       </c>
       <c r="C155" s="24" t="str">
@@ -7606,10 +7606,10 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="s">
+      <c r="A156" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B156" s="2" t="n">
+      <c r="B156" s="8" t="n">
         <v>66</v>
       </c>
       <c r="C156" s="24" t="str">
@@ -7624,10 +7624,10 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1" t="s">
+      <c r="A157" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B157" s="2" t="n">
+      <c r="B157" s="8" t="n">
         <v>67</v>
       </c>
       <c r="C157" s="24" t="str">
@@ -7642,10 +7642,10 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="s">
+      <c r="A158" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B158" s="2" t="n">
+      <c r="B158" s="8" t="n">
         <v>68</v>
       </c>
       <c r="C158" s="24" t="str">
@@ -7675,10 +7675,10 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="s">
+      <c r="A160" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B160" s="2" t="n">
+      <c r="B160" s="8" t="n">
         <v>70</v>
       </c>
       <c r="C160" s="25" t="str">
@@ -7693,10 +7693,10 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="s">
+      <c r="A161" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B161" s="2" t="n">
+      <c r="B161" s="8" t="n">
         <v>71</v>
       </c>
       <c r="C161" s="25" t="str">
@@ -7762,10 +7762,10 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="s">
+      <c r="A165" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B165" s="2" t="n">
+      <c r="B165" s="8" t="n">
         <v>75</v>
       </c>
       <c r="C165" s="25" t="str">
@@ -7780,10 +7780,10 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="1" t="s">
+      <c r="A166" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B166" s="2" t="n">
+      <c r="B166" s="8" t="n">
         <v>76</v>
       </c>
       <c r="C166" s="23" t="str">
@@ -7795,10 +7795,10 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1" t="s">
+      <c r="A167" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B167" s="2" t="n">
+      <c r="B167" s="8" t="n">
         <v>77</v>
       </c>
       <c r="C167" s="23" t="str">
@@ -7810,10 +7810,10 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="1" t="s">
+      <c r="A168" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B168" s="2" t="n">
+      <c r="B168" s="8" t="n">
         <v>78</v>
       </c>
       <c r="C168" s="25" t="str">
@@ -7828,10 +7828,10 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="1" t="s">
+      <c r="A169" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B169" s="2" t="n">
+      <c r="B169" s="8" t="n">
         <v>79</v>
       </c>
       <c r="C169" s="25" t="str">
@@ -7864,10 +7864,10 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="1" t="s">
+      <c r="A171" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B171" s="2" t="n">
+      <c r="B171" s="8" t="n">
         <v>81</v>
       </c>
       <c r="C171" s="25" t="str">
@@ -7882,10 +7882,10 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="1" t="s">
+      <c r="A172" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B172" s="2" t="n">
+      <c r="B172" s="8" t="n">
         <v>82</v>
       </c>
       <c r="C172" s="25" t="str">
@@ -7900,10 +7900,10 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="1" t="s">
+      <c r="A173" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B173" s="2" t="n">
+      <c r="B173" s="8" t="n">
         <v>83</v>
       </c>
       <c r="C173" s="25" t="str">
@@ -7954,10 +7954,10 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="1" t="s">
+      <c r="A176" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B176" s="2" t="n">
+      <c r="B176" s="8" t="n">
         <v>86</v>
       </c>
       <c r="C176" s="23" t="str">
@@ -7969,10 +7969,10 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="1" t="s">
+      <c r="A177" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B177" s="2" t="n">
+      <c r="B177" s="8" t="n">
         <v>87</v>
       </c>
       <c r="C177" s="24" t="str">
@@ -7987,10 +7987,10 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="1" t="s">
+      <c r="A178" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B178" s="2" t="n">
+      <c r="B178" s="8" t="n">
         <v>88</v>
       </c>
       <c r="C178" s="25" t="str">
@@ -8005,10 +8005,10 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="1" t="s">
+      <c r="A179" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B179" s="2" t="n">
+      <c r="B179" s="8" t="n">
         <v>89</v>
       </c>
       <c r="C179" s="10" t="s">
@@ -8087,10 +8087,10 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="1" t="s">
+      <c r="A184" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B184" s="2" t="n">
+      <c r="B184" s="8" t="n">
         <v>94</v>
       </c>
       <c r="C184" s="10" t="s">
@@ -8635,10 +8635,10 @@
       </c>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="1" t="s">
+      <c r="A213" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B213" s="2" t="n">
+      <c r="B213" s="8" t="n">
         <v>13</v>
       </c>
       <c r="C213" s="23" t="str">
@@ -12868,10 +12868,10 @@
       </c>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A446" s="1" t="s">
+      <c r="A446" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="B446" s="2" t="n">
+      <c r="B446" s="8" t="n">
         <v>29</v>
       </c>
       <c r="C446" s="37" t="str">
@@ -13344,10 +13344,10 @@
       </c>
     </row>
     <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A471" s="1" t="s">
+      <c r="A471" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B471" s="2" t="n">
+      <c r="B471" s="8" t="n">
         <v>17</v>
       </c>
       <c r="C471" s="25" t="str">
@@ -13521,10 +13521,10 @@
       </c>
     </row>
     <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A481" s="1" t="s">
+      <c r="A481" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B481" s="2" t="n">
+      <c r="B481" s="8" t="n">
         <v>27</v>
       </c>
       <c r="C481" s="25" t="str">
@@ -14350,10 +14350,10 @@
       </c>
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A530" s="1" t="s">
+      <c r="A530" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="B530" s="2" t="n">
+      <c r="B530" s="8" t="n">
         <v>88</v>
       </c>
       <c r="C530" s="37" t="str">

--- a/list of gates updated.xlsx
+++ b/list of gates updated.xlsx
@@ -31295,11 +31295,11 @@
         <v>1164</v>
       </c>
       <c r="B1517" s="8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C1517" s="71" t="str">
         <f aca="false">CONCATENATE(A1517,B1517)</f>
-        <v>AX0</v>
+        <v>AX18</v>
       </c>
       <c r="D1517" s="1" t="n">
         <v>15</v>
@@ -31312,10 +31312,10 @@
       </c>
     </row>
     <row r="1518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1518" s="1" t="s">
+      <c r="A1518" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1518" s="2" t="n">
+      <c r="B1518" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C1518" s="71" t="str">
@@ -31330,10 +31330,10 @@
       </c>
     </row>
     <row r="1519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1519" s="1" t="s">
+      <c r="A1519" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1519" s="2" t="n">
+      <c r="B1519" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C1519" s="71" t="str">
@@ -31348,10 +31348,10 @@
       </c>
     </row>
     <row r="1520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1520" s="1" t="s">
+      <c r="A1520" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1520" s="2" t="n">
+      <c r="B1520" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C1520" s="71" t="str">
@@ -31366,10 +31366,10 @@
       </c>
     </row>
     <row r="1521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1521" s="1" t="s">
+      <c r="A1521" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1521" s="2" t="n">
+      <c r="B1521" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C1521" s="71" t="str">
@@ -31384,10 +31384,10 @@
       </c>
     </row>
     <row r="1522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1522" s="1" t="s">
+      <c r="A1522" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1522" s="2" t="n">
+      <c r="B1522" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C1522" s="71" t="str">
@@ -31402,10 +31402,10 @@
       </c>
     </row>
     <row r="1523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1523" s="1" t="s">
+      <c r="A1523" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1523" s="2" t="n">
+      <c r="B1523" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C1523" s="71" t="str">
@@ -31420,10 +31420,10 @@
       </c>
     </row>
     <row r="1524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1524" s="1" t="s">
+      <c r="A1524" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1524" s="2" t="n">
+      <c r="B1524" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C1524" s="71" t="str">
@@ -31438,10 +31438,10 @@
       </c>
     </row>
     <row r="1525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1525" s="1" t="s">
+      <c r="A1525" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1525" s="2" t="n">
+      <c r="B1525" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C1525" s="71" t="str">
@@ -31456,10 +31456,10 @@
       </c>
     </row>
     <row r="1526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1526" s="1" t="s">
+      <c r="A1526" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1526" s="2" t="n">
+      <c r="B1526" s="8" t="n">
         <v>9</v>
       </c>
       <c r="C1526" s="71" t="str">
@@ -31474,10 +31474,10 @@
       </c>
     </row>
     <row r="1527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1527" s="1" t="s">
+      <c r="A1527" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1527" s="2" t="n">
+      <c r="B1527" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C1527" s="71" t="str">
@@ -31492,10 +31492,10 @@
       </c>
     </row>
     <row r="1528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1528" s="1" t="s">
+      <c r="A1528" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1528" s="2" t="n">
+      <c r="B1528" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C1528" s="71" t="str">
@@ -31510,10 +31510,10 @@
       </c>
     </row>
     <row r="1529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1529" s="1" t="s">
+      <c r="A1529" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1529" s="2" t="n">
+      <c r="B1529" s="8" t="n">
         <v>12</v>
       </c>
       <c r="C1529" s="71" t="str">
@@ -31528,10 +31528,10 @@
       </c>
     </row>
     <row r="1530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1530" s="1" t="s">
+      <c r="A1530" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1530" s="2" t="n">
+      <c r="B1530" s="8" t="n">
         <v>13</v>
       </c>
       <c r="C1530" s="71" t="str">
@@ -31546,10 +31546,10 @@
       </c>
     </row>
     <row r="1531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1531" s="1" t="s">
+      <c r="A1531" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1531" s="2" t="n">
+      <c r="B1531" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C1531" s="71" t="str">
@@ -31564,10 +31564,10 @@
       </c>
     </row>
     <row r="1532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1532" s="1" t="s">
+      <c r="A1532" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1532" s="2" t="n">
+      <c r="B1532" s="8" t="n">
         <v>15</v>
       </c>
       <c r="C1532" s="71" t="str">
@@ -31582,10 +31582,10 @@
       </c>
     </row>
     <row r="1533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1533" s="1" t="s">
+      <c r="A1533" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1533" s="2" t="n">
+      <c r="B1533" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C1533" s="71" t="str">
@@ -31600,10 +31600,10 @@
       </c>
     </row>
     <row r="1534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1534" s="1" t="s">
+      <c r="A1534" s="7" t="s">
         <v>1166</v>
       </c>
-      <c r="B1534" s="2" t="n">
+      <c r="B1534" s="8" t="n">
         <v>17</v>
       </c>
       <c r="C1534" s="71" t="str">
@@ -31621,10 +31621,10 @@
       </c>
     </row>
     <row r="1535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1535" s="1" t="s">
+      <c r="A1535" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1535" s="2" t="n">
+      <c r="B1535" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C1535" s="71" t="str">
@@ -31639,10 +31639,10 @@
       </c>
     </row>
     <row r="1536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1536" s="1" t="s">
+      <c r="A1536" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1536" s="2" t="n">
+      <c r="B1536" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C1536" s="71" t="str">
@@ -31657,10 +31657,10 @@
       </c>
     </row>
     <row r="1537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1537" s="1" t="s">
+      <c r="A1537" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1537" s="2" t="n">
+      <c r="B1537" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C1537" s="71" t="str">
@@ -31675,10 +31675,10 @@
       </c>
     </row>
     <row r="1538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1538" s="1" t="s">
+      <c r="A1538" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1538" s="2" t="n">
+      <c r="B1538" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C1538" s="71" t="str">
@@ -31693,10 +31693,10 @@
       </c>
     </row>
     <row r="1539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1539" s="1" t="s">
+      <c r="A1539" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1539" s="2" t="n">
+      <c r="B1539" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C1539" s="71" t="str">
@@ -31711,10 +31711,10 @@
       </c>
     </row>
     <row r="1540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1540" s="1" t="s">
+      <c r="A1540" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1540" s="2" t="n">
+      <c r="B1540" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C1540" s="71" t="str">
@@ -31729,10 +31729,10 @@
       </c>
     </row>
     <row r="1541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1541" s="1" t="s">
+      <c r="A1541" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1541" s="2" t="n">
+      <c r="B1541" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C1541" s="71" t="str">
@@ -31747,10 +31747,10 @@
       </c>
     </row>
     <row r="1542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1542" s="1" t="s">
+      <c r="A1542" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1542" s="2" t="n">
+      <c r="B1542" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C1542" s="71" t="str">
@@ -31765,10 +31765,10 @@
       </c>
     </row>
     <row r="1543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1543" s="1" t="s">
+      <c r="A1543" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1543" s="2" t="n">
+      <c r="B1543" s="8" t="n">
         <v>9</v>
       </c>
       <c r="C1543" s="71" t="str">
@@ -31783,10 +31783,10 @@
       </c>
     </row>
     <row r="1544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1544" s="1" t="s">
+      <c r="A1544" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1544" s="2" t="n">
+      <c r="B1544" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C1544" s="71" t="str">
@@ -31801,10 +31801,10 @@
       </c>
     </row>
     <row r="1545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1545" s="1" t="s">
+      <c r="A1545" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1545" s="2" t="n">
+      <c r="B1545" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C1545" s="71" t="str">
@@ -31819,10 +31819,10 @@
       </c>
     </row>
     <row r="1546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1546" s="1" t="s">
+      <c r="A1546" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1546" s="2" t="n">
+      <c r="B1546" s="8" t="n">
         <v>13</v>
       </c>
       <c r="C1546" s="71" t="str">
@@ -31837,10 +31837,10 @@
       </c>
     </row>
     <row r="1547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1547" s="1" t="s">
+      <c r="A1547" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1547" s="2" t="n">
+      <c r="B1547" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C1547" s="71" t="str">
@@ -31855,10 +31855,10 @@
       </c>
     </row>
     <row r="1548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1548" s="1" t="s">
+      <c r="A1548" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1548" s="2" t="n">
+      <c r="B1548" s="8" t="n">
         <v>15</v>
       </c>
       <c r="C1548" s="71" t="str">
@@ -31873,10 +31873,10 @@
       </c>
     </row>
     <row r="1549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1549" s="1" t="s">
+      <c r="A1549" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1549" s="2" t="n">
+      <c r="B1549" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C1549" s="71" t="str">
@@ -31891,10 +31891,10 @@
       </c>
     </row>
     <row r="1550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1550" s="1" t="s">
+      <c r="A1550" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="B1550" s="2" t="n">
+      <c r="B1550" s="8" t="n">
         <v>17</v>
       </c>
       <c r="C1550" s="71" t="str">
@@ -31912,10 +31912,10 @@
       </c>
     </row>
     <row r="1551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1551" s="1" t="s">
+      <c r="A1551" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1551" s="2" t="n">
+      <c r="B1551" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C1551" s="74" t="str">
@@ -31930,10 +31930,10 @@
       </c>
     </row>
     <row r="1552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1552" s="1" t="s">
+      <c r="A1552" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1552" s="2" t="n">
+      <c r="B1552" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C1552" s="74" t="str">
@@ -31948,10 +31948,10 @@
       </c>
     </row>
     <row r="1553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1553" s="1" t="s">
+      <c r="A1553" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1553" s="2" t="n">
+      <c r="B1553" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C1553" s="74" t="str">
@@ -31966,10 +31966,10 @@
       </c>
     </row>
     <row r="1554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1554" s="1" t="s">
+      <c r="A1554" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1554" s="2" t="n">
+      <c r="B1554" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C1554" s="74" t="str">
@@ -31984,10 +31984,10 @@
       </c>
     </row>
     <row r="1555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1555" s="1" t="s">
+      <c r="A1555" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1555" s="2" t="n">
+      <c r="B1555" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C1555" s="74" t="str">
@@ -32002,10 +32002,10 @@
       </c>
     </row>
     <row r="1556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1556" s="1" t="s">
+      <c r="A1556" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1556" s="2" t="n">
+      <c r="B1556" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C1556" s="74" t="str">
@@ -32020,10 +32020,10 @@
       </c>
     </row>
     <row r="1557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1557" s="1" t="s">
+      <c r="A1557" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1557" s="2" t="n">
+      <c r="B1557" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C1557" s="74" t="str">
@@ -32038,10 +32038,10 @@
       </c>
     </row>
     <row r="1558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1558" s="1" t="s">
+      <c r="A1558" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1558" s="2" t="n">
+      <c r="B1558" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C1558" s="74" t="str">
@@ -32056,10 +32056,10 @@
       </c>
     </row>
     <row r="1559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1559" s="1" t="s">
+      <c r="A1559" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1559" s="2" t="n">
+      <c r="B1559" s="8" t="n">
         <v>9</v>
       </c>
       <c r="C1559" s="74" t="str">
@@ -32074,10 +32074,10 @@
       </c>
     </row>
     <row r="1560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1560" s="1" t="s">
+      <c r="A1560" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1560" s="2" t="n">
+      <c r="B1560" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C1560" s="74" t="str">
@@ -32092,10 +32092,10 @@
       </c>
     </row>
     <row r="1561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1561" s="1" t="s">
+      <c r="A1561" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1561" s="2" t="n">
+      <c r="B1561" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C1561" s="74" t="str">
@@ -32110,10 +32110,10 @@
       </c>
     </row>
     <row r="1562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1562" s="1" t="s">
+      <c r="A1562" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1562" s="2" t="n">
+      <c r="B1562" s="8" t="n">
         <v>12</v>
       </c>
       <c r="C1562" s="74" t="str">
@@ -32128,10 +32128,10 @@
       </c>
     </row>
     <row r="1563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1563" s="1" t="s">
+      <c r="A1563" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1563" s="2" t="n">
+      <c r="B1563" s="8" t="n">
         <v>13</v>
       </c>
       <c r="C1563" s="74" t="str">
@@ -32146,10 +32146,10 @@
       </c>
     </row>
     <row r="1564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1564" s="1" t="s">
+      <c r="A1564" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1564" s="2" t="n">
+      <c r="B1564" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C1564" s="74" t="str">
@@ -32164,10 +32164,10 @@
       </c>
     </row>
     <row r="1565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1565" s="1" t="s">
+      <c r="A1565" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1565" s="2" t="n">
+      <c r="B1565" s="8" t="n">
         <v>15</v>
       </c>
       <c r="C1565" s="74" t="str">
@@ -32182,10 +32182,10 @@
       </c>
     </row>
     <row r="1566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1566" s="1" t="s">
+      <c r="A1566" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1566" s="2" t="n">
+      <c r="B1566" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C1566" s="74" t="str">
@@ -32200,10 +32200,10 @@
       </c>
     </row>
     <row r="1567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1567" s="1" t="s">
+      <c r="A1567" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="B1567" s="2" t="n">
+      <c r="B1567" s="8" t="n">
         <v>17</v>
       </c>
       <c r="C1567" s="74" t="str">
@@ -32221,10 +32221,10 @@
       </c>
     </row>
     <row r="1568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1568" s="1" t="s">
+      <c r="A1568" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1568" s="2" t="n">
+      <c r="B1568" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C1568" s="74" t="str">
@@ -32239,10 +32239,10 @@
       </c>
     </row>
     <row r="1569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1569" s="1" t="s">
+      <c r="A1569" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1569" s="2" t="n">
+      <c r="B1569" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C1569" s="74" t="str">
@@ -32257,10 +32257,10 @@
       </c>
     </row>
     <row r="1570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1570" s="1" t="s">
+      <c r="A1570" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1570" s="2" t="n">
+      <c r="B1570" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C1570" s="74" t="str">
@@ -32275,10 +32275,10 @@
       </c>
     </row>
     <row r="1571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1571" s="1" t="s">
+      <c r="A1571" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1571" s="2" t="n">
+      <c r="B1571" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C1571" s="74" t="str">
@@ -32293,10 +32293,10 @@
       </c>
     </row>
     <row r="1572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1572" s="1" t="s">
+      <c r="A1572" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1572" s="2" t="n">
+      <c r="B1572" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C1572" s="74" t="str">
@@ -32311,10 +32311,10 @@
       </c>
     </row>
     <row r="1573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1573" s="1" t="s">
+      <c r="A1573" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1573" s="2" t="n">
+      <c r="B1573" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C1573" s="74" t="str">
@@ -32329,10 +32329,10 @@
       </c>
     </row>
     <row r="1574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1574" s="1" t="s">
+      <c r="A1574" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1574" s="2" t="n">
+      <c r="B1574" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C1574" s="74" t="str">
@@ -32347,10 +32347,10 @@
       </c>
     </row>
     <row r="1575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1575" s="1" t="s">
+      <c r="A1575" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1575" s="2" t="n">
+      <c r="B1575" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C1575" s="74" t="str">
@@ -32365,10 +32365,10 @@
       </c>
     </row>
     <row r="1576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1576" s="1" t="s">
+      <c r="A1576" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1576" s="2" t="n">
+      <c r="B1576" s="8" t="n">
         <v>9</v>
       </c>
       <c r="C1576" s="74" t="str">
@@ -32383,10 +32383,10 @@
       </c>
     </row>
     <row r="1577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1577" s="1" t="s">
+      <c r="A1577" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1577" s="2" t="n">
+      <c r="B1577" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C1577" s="74" t="str">
@@ -32401,10 +32401,10 @@
       </c>
     </row>
     <row r="1578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1578" s="1" t="s">
+      <c r="A1578" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1578" s="2" t="n">
+      <c r="B1578" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C1578" s="74" t="str">
@@ -32419,10 +32419,10 @@
       </c>
     </row>
     <row r="1579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1579" s="1" t="s">
+      <c r="A1579" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1579" s="2" t="n">
+      <c r="B1579" s="8" t="n">
         <v>12</v>
       </c>
       <c r="C1579" s="74" t="str">
@@ -32437,10 +32437,10 @@
       </c>
     </row>
     <row r="1580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1580" s="1" t="s">
+      <c r="A1580" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1580" s="2" t="n">
+      <c r="B1580" s="8" t="n">
         <v>13</v>
       </c>
       <c r="C1580" s="74" t="str">
@@ -32455,10 +32455,10 @@
       </c>
     </row>
     <row r="1581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1581" s="1" t="s">
+      <c r="A1581" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1581" s="2" t="n">
+      <c r="B1581" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C1581" s="74" t="str">
@@ -32473,10 +32473,10 @@
       </c>
     </row>
     <row r="1582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1582" s="1" t="s">
+      <c r="A1582" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1582" s="2" t="n">
+      <c r="B1582" s="8" t="n">
         <v>15</v>
       </c>
       <c r="C1582" s="74" t="str">
@@ -32491,10 +32491,10 @@
       </c>
     </row>
     <row r="1583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1583" s="1" t="s">
+      <c r="A1583" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1583" s="2" t="n">
+      <c r="B1583" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C1583" s="74" t="str">
@@ -32509,10 +32509,10 @@
       </c>
     </row>
     <row r="1584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1584" s="1" t="s">
+      <c r="A1584" s="7" t="s">
         <v>1172</v>
       </c>
-      <c r="B1584" s="2" t="n">
+      <c r="B1584" s="8" t="n">
         <v>17</v>
       </c>
       <c r="C1584" s="74" t="str">
@@ -32530,10 +32530,10 @@
       </c>
     </row>
     <row r="1585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1585" s="1" t="s">
+      <c r="A1585" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1585" s="2" t="n">
+      <c r="B1585" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C1585" s="74" t="str">
@@ -32548,10 +32548,10 @@
       </c>
     </row>
     <row r="1586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1586" s="1" t="s">
+      <c r="A1586" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1586" s="2" t="n">
+      <c r="B1586" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C1586" s="74" t="str">
@@ -32566,10 +32566,10 @@
       </c>
     </row>
     <row r="1587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1587" s="1" t="s">
+      <c r="A1587" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1587" s="2" t="n">
+      <c r="B1587" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C1587" s="74" t="str">
@@ -32584,10 +32584,10 @@
       </c>
     </row>
     <row r="1588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1588" s="1" t="s">
+      <c r="A1588" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1588" s="2" t="n">
+      <c r="B1588" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C1588" s="74" t="str">
@@ -32602,10 +32602,10 @@
       </c>
     </row>
     <row r="1589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1589" s="1" t="s">
+      <c r="A1589" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1589" s="2" t="n">
+      <c r="B1589" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C1589" s="74" t="str">
@@ -32620,10 +32620,10 @@
       </c>
     </row>
     <row r="1590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1590" s="1" t="s">
+      <c r="A1590" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1590" s="2" t="n">
+      <c r="B1590" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C1590" s="74" t="str">
@@ -32638,10 +32638,10 @@
       </c>
     </row>
     <row r="1591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1591" s="1" t="s">
+      <c r="A1591" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1591" s="2" t="n">
+      <c r="B1591" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C1591" s="74" t="str">
@@ -32656,10 +32656,10 @@
       </c>
     </row>
     <row r="1592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1592" s="1" t="s">
+      <c r="A1592" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1592" s="2" t="n">
+      <c r="B1592" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C1592" s="74" t="str">
@@ -32674,10 +32674,10 @@
       </c>
     </row>
     <row r="1593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1593" s="1" t="s">
+      <c r="A1593" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1593" s="2" t="n">
+      <c r="B1593" s="8" t="n">
         <v>9</v>
       </c>
       <c r="C1593" s="74" t="str">
@@ -32692,10 +32692,10 @@
       </c>
     </row>
     <row r="1594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1594" s="1" t="s">
+      <c r="A1594" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1594" s="2" t="n">
+      <c r="B1594" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C1594" s="74" t="str">
@@ -32710,10 +32710,10 @@
       </c>
     </row>
     <row r="1595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1595" s="1" t="s">
+      <c r="A1595" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1595" s="2" t="n">
+      <c r="B1595" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C1595" s="74" t="str">
@@ -32728,10 +32728,10 @@
       </c>
     </row>
     <row r="1596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1596" s="1" t="s">
+      <c r="A1596" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1596" s="2" t="n">
+      <c r="B1596" s="8" t="n">
         <v>12</v>
       </c>
       <c r="C1596" s="74" t="str">
@@ -32746,10 +32746,10 @@
       </c>
     </row>
     <row r="1597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1597" s="1" t="s">
+      <c r="A1597" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1597" s="2" t="n">
+      <c r="B1597" s="8" t="n">
         <v>13</v>
       </c>
       <c r="C1597" s="74" t="str">
@@ -32764,10 +32764,10 @@
       </c>
     </row>
     <row r="1598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1598" s="1" t="s">
+      <c r="A1598" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1598" s="2" t="n">
+      <c r="B1598" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C1598" s="74" t="str">
@@ -32782,10 +32782,10 @@
       </c>
     </row>
     <row r="1599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1599" s="1" t="s">
+      <c r="A1599" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1599" s="2" t="n">
+      <c r="B1599" s="8" t="n">
         <v>15</v>
       </c>
       <c r="C1599" s="74" t="str">
@@ -32800,10 +32800,10 @@
       </c>
     </row>
     <row r="1600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1600" s="1" t="s">
+      <c r="A1600" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1600" s="2" t="n">
+      <c r="B1600" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C1600" s="74" t="str">
@@ -32818,10 +32818,10 @@
       </c>
     </row>
     <row r="1601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1601" s="1" t="s">
+      <c r="A1601" s="7" t="s">
         <v>1174</v>
       </c>
-      <c r="B1601" s="2" t="n">
+      <c r="B1601" s="8" t="n">
         <v>17</v>
       </c>
       <c r="C1601" s="74" t="str">
@@ -32839,10 +32839,10 @@
       </c>
     </row>
     <row r="1602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1602" s="1" t="s">
+      <c r="A1602" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1602" s="2" t="n">
+      <c r="B1602" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C1602" s="74" t="str">
@@ -32857,10 +32857,10 @@
       </c>
     </row>
     <row r="1603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1603" s="1" t="s">
+      <c r="A1603" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1603" s="2" t="n">
+      <c r="B1603" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C1603" s="74" t="str">
@@ -32875,10 +32875,10 @@
       </c>
     </row>
     <row r="1604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1604" s="1" t="s">
+      <c r="A1604" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1604" s="2" t="n">
+      <c r="B1604" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C1604" s="74" t="str">
@@ -32893,10 +32893,10 @@
       </c>
     </row>
     <row r="1605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1605" s="1" t="s">
+      <c r="A1605" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1605" s="2" t="n">
+      <c r="B1605" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C1605" s="74" t="str">
@@ -32911,10 +32911,10 @@
       </c>
     </row>
     <row r="1606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1606" s="1" t="s">
+      <c r="A1606" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1606" s="2" t="n">
+      <c r="B1606" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C1606" s="74" t="str">
@@ -32929,10 +32929,10 @@
       </c>
     </row>
     <row r="1607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1607" s="1" t="s">
+      <c r="A1607" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1607" s="2" t="n">
+      <c r="B1607" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C1607" s="74" t="str">
@@ -32947,10 +32947,10 @@
       </c>
     </row>
     <row r="1608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1608" s="1" t="s">
+      <c r="A1608" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1608" s="2" t="n">
+      <c r="B1608" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C1608" s="74" t="str">
@@ -32965,10 +32965,10 @@
       </c>
     </row>
     <row r="1609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1609" s="1" t="s">
+      <c r="A1609" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1609" s="2" t="n">
+      <c r="B1609" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C1609" s="74" t="str">
@@ -32983,10 +32983,10 @@
       </c>
     </row>
     <row r="1610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1610" s="1" t="s">
+      <c r="A1610" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1610" s="2" t="n">
+      <c r="B1610" s="8" t="n">
         <v>9</v>
       </c>
       <c r="C1610" s="74" t="str">
@@ -33001,10 +33001,10 @@
       </c>
     </row>
     <row r="1611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1611" s="1" t="s">
+      <c r="A1611" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1611" s="2" t="n">
+      <c r="B1611" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C1611" s="74" t="str">
@@ -33019,10 +33019,10 @@
       </c>
     </row>
     <row r="1612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1612" s="1" t="s">
+      <c r="A1612" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1612" s="2" t="n">
+      <c r="B1612" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C1612" s="74" t="str">
@@ -33037,10 +33037,10 @@
       </c>
     </row>
     <row r="1613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1613" s="1" t="s">
+      <c r="A1613" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1613" s="2" t="n">
+      <c r="B1613" s="8" t="n">
         <v>12</v>
       </c>
       <c r="C1613" s="74" t="str">
@@ -33055,10 +33055,10 @@
       </c>
     </row>
     <row r="1614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1614" s="1" t="s">
+      <c r="A1614" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1614" s="2" t="n">
+      <c r="B1614" s="8" t="n">
         <v>13</v>
       </c>
       <c r="C1614" s="74" t="str">
@@ -33073,10 +33073,10 @@
       </c>
     </row>
     <row r="1615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1615" s="1" t="s">
+      <c r="A1615" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1615" s="2" t="n">
+      <c r="B1615" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C1615" s="74" t="str">
@@ -33091,10 +33091,10 @@
       </c>
     </row>
     <row r="1616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1616" s="1" t="s">
+      <c r="A1616" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1616" s="2" t="n">
+      <c r="B1616" s="8" t="n">
         <v>15</v>
       </c>
       <c r="C1616" s="74" t="str">
@@ -33109,10 +33109,10 @@
       </c>
     </row>
     <row r="1617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1617" s="1" t="s">
+      <c r="A1617" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1617" s="2" t="n">
+      <c r="B1617" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C1617" s="74" t="str">
@@ -33127,10 +33127,10 @@
       </c>
     </row>
     <row r="1618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1618" s="1" t="s">
+      <c r="A1618" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B1618" s="2" t="n">
+      <c r="B1618" s="8" t="n">
         <v>17</v>
       </c>
       <c r="C1618" s="74" t="str">
@@ -33148,10 +33148,10 @@
       </c>
     </row>
     <row r="1619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1619" s="1" t="s">
+      <c r="A1619" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1619" s="2" t="n">
+      <c r="B1619" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C1619" s="74" t="str">
@@ -33166,10 +33166,10 @@
       </c>
     </row>
     <row r="1620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1620" s="1" t="s">
+      <c r="A1620" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1620" s="2" t="n">
+      <c r="B1620" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C1620" s="74" t="str">
@@ -33184,10 +33184,10 @@
       </c>
     </row>
     <row r="1621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1621" s="1" t="s">
+      <c r="A1621" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1621" s="2" t="n">
+      <c r="B1621" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C1621" s="74" t="str">
@@ -33202,10 +33202,10 @@
       </c>
     </row>
     <row r="1622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1622" s="1" t="s">
+      <c r="A1622" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1622" s="2" t="n">
+      <c r="B1622" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C1622" s="74" t="str">
@@ -33220,10 +33220,10 @@
       </c>
     </row>
     <row r="1623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1623" s="1" t="s">
+      <c r="A1623" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1623" s="2" t="n">
+      <c r="B1623" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C1623" s="74" t="str">
@@ -33238,10 +33238,10 @@
       </c>
     </row>
     <row r="1624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1624" s="1" t="s">
+      <c r="A1624" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1624" s="2" t="n">
+      <c r="B1624" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C1624" s="74" t="str">
@@ -33256,10 +33256,10 @@
       </c>
     </row>
     <row r="1625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1625" s="1" t="s">
+      <c r="A1625" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1625" s="2" t="n">
+      <c r="B1625" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C1625" s="74" t="str">
@@ -33274,10 +33274,10 @@
       </c>
     </row>
     <row r="1626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1626" s="1" t="s">
+      <c r="A1626" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1626" s="2" t="n">
+      <c r="B1626" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C1626" s="74" t="str">
@@ -33292,10 +33292,10 @@
       </c>
     </row>
     <row r="1627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1627" s="1" t="s">
+      <c r="A1627" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1627" s="2" t="n">
+      <c r="B1627" s="8" t="n">
         <v>9</v>
       </c>
       <c r="C1627" s="74" t="str">
@@ -33310,10 +33310,10 @@
       </c>
     </row>
     <row r="1628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1628" s="1" t="s">
+      <c r="A1628" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1628" s="2" t="n">
+      <c r="B1628" s="8" t="n">
         <v>10</v>
       </c>
       <c r="C1628" s="74" t="str">
@@ -33328,10 +33328,10 @@
       </c>
     </row>
     <row r="1629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1629" s="1" t="s">
+      <c r="A1629" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1629" s="2" t="n">
+      <c r="B1629" s="8" t="n">
         <v>11</v>
       </c>
       <c r="C1629" s="74" t="str">
@@ -33346,10 +33346,10 @@
       </c>
     </row>
     <row r="1630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1630" s="1" t="s">
+      <c r="A1630" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1630" s="2" t="n">
+      <c r="B1630" s="8" t="n">
         <v>12</v>
       </c>
       <c r="C1630" s="74" t="str">
@@ -33364,10 +33364,10 @@
       </c>
     </row>
     <row r="1631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1631" s="1" t="s">
+      <c r="A1631" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1631" s="2" t="n">
+      <c r="B1631" s="8" t="n">
         <v>13</v>
       </c>
       <c r="C1631" s="74" t="str">
@@ -33382,10 +33382,10 @@
       </c>
     </row>
     <row r="1632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1632" s="1" t="s">
+      <c r="A1632" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1632" s="2" t="n">
+      <c r="B1632" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C1632" s="74" t="str">
@@ -33400,10 +33400,10 @@
       </c>
     </row>
     <row r="1633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1633" s="1" t="s">
+      <c r="A1633" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1633" s="2" t="n">
+      <c r="B1633" s="8" t="n">
         <v>15</v>
       </c>
       <c r="C1633" s="74" t="str">
@@ -33418,10 +33418,10 @@
       </c>
     </row>
     <row r="1634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1634" s="1" t="s">
+      <c r="A1634" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1634" s="2" t="n">
+      <c r="B1634" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C1634" s="74" t="str">
@@ -33436,10 +33436,10 @@
       </c>
     </row>
     <row r="1635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1635" s="1" t="s">
+      <c r="A1635" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="B1635" s="2" t="n">
+      <c r="B1635" s="8" t="n">
         <v>17</v>
       </c>
       <c r="C1635" s="74" t="str">

--- a/list of gates updated.xlsx
+++ b/list of gates updated.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4886" uniqueCount="1271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4870" uniqueCount="1271">
   <si>
     <t xml:space="preserve">Area</t>
   </si>
@@ -4637,15 +4637,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="36" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="39" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4750,7 +4750,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G2012"/>
+  <dimension ref="A1:G1996"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.25"/>
@@ -24068,10 +24068,10 @@
       </c>
     </row>
     <row r="1068" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1068" s="10" t="s">
+      <c r="A1068" s="7" t="s">
         <v>1078</v>
       </c>
-      <c r="B1068" s="2" t="n">
+      <c r="B1068" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C1068" s="23" t="str">
@@ -24080,10 +24080,10 @@
       </c>
     </row>
     <row r="1069" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1069" s="10" t="s">
+      <c r="A1069" s="7" t="s">
         <v>1078</v>
       </c>
-      <c r="B1069" s="2" t="n">
+      <c r="B1069" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C1069" s="23" t="str">
@@ -33709,10 +33709,10 @@
       </c>
     </row>
     <row r="1646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1646" s="1" t="s">
+      <c r="A1646" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1646" s="2" t="n">
+      <c r="B1646" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C1646" s="77" t="str">
@@ -33727,10 +33727,10 @@
       </c>
     </row>
     <row r="1647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1647" s="1" t="s">
+      <c r="A1647" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1647" s="2" t="n">
+      <c r="B1647" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C1647" s="77" t="str">
@@ -33745,10 +33745,10 @@
       </c>
     </row>
     <row r="1648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1648" s="1" t="s">
+      <c r="A1648" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1648" s="2" t="n">
+      <c r="B1648" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C1648" s="77" t="str">
@@ -33763,10 +33763,10 @@
       </c>
     </row>
     <row r="1649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1649" s="1" t="s">
+      <c r="A1649" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1649" s="2" t="n">
+      <c r="B1649" s="8" t="n">
         <v>7</v>
       </c>
       <c r="C1649" s="77" t="str">
@@ -33781,10 +33781,10 @@
       </c>
     </row>
     <row r="1650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1650" s="1" t="s">
+      <c r="A1650" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1650" s="2" t="n">
+      <c r="B1650" s="8" t="n">
         <v>8</v>
       </c>
       <c r="C1650" s="77" t="str">
@@ -33853,10 +33853,10 @@
       </c>
     </row>
     <row r="1654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1654" s="1" t="s">
+      <c r="A1654" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1654" s="2" t="n">
+      <c r="B1654" s="8" t="n">
         <v>12</v>
       </c>
       <c r="C1654" s="77" t="str">
@@ -33871,10 +33871,10 @@
       </c>
     </row>
     <row r="1655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1655" s="1" t="s">
+      <c r="A1655" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1655" s="2" t="n">
+      <c r="B1655" s="8" t="n">
         <v>13</v>
       </c>
       <c r="C1655" s="77" t="str">
@@ -33889,10 +33889,10 @@
       </c>
     </row>
     <row r="1656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1656" s="1" t="s">
+      <c r="A1656" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1656" s="2" t="n">
+      <c r="B1656" s="8" t="n">
         <v>14</v>
       </c>
       <c r="C1656" s="77" t="str">
@@ -33907,10 +33907,10 @@
       </c>
     </row>
     <row r="1657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1657" s="1" t="s">
+      <c r="A1657" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1657" s="2" t="n">
+      <c r="B1657" s="8" t="n">
         <v>15</v>
       </c>
       <c r="C1657" s="77" t="str">
@@ -33925,10 +33925,10 @@
       </c>
     </row>
     <row r="1658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1658" s="1" t="s">
+      <c r="A1658" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1658" s="2" t="n">
+      <c r="B1658" s="8" t="n">
         <v>16</v>
       </c>
       <c r="C1658" s="77" t="str">
@@ -33943,10 +33943,10 @@
       </c>
     </row>
     <row r="1659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1659" s="1" t="s">
+      <c r="A1659" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1659" s="2" t="n">
+      <c r="B1659" s="8" t="n">
         <v>17</v>
       </c>
       <c r="C1659" s="78" t="str">
@@ -33961,10 +33961,10 @@
       </c>
     </row>
     <row r="1660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1660" s="1" t="s">
+      <c r="A1660" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1660" s="2" t="n">
+      <c r="B1660" s="8" t="n">
         <v>18</v>
       </c>
       <c r="C1660" s="78" t="str">
@@ -33979,10 +33979,10 @@
       </c>
     </row>
     <row r="1661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1661" s="1" t="s">
+      <c r="A1661" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1661" s="2" t="n">
+      <c r="B1661" s="8" t="n">
         <v>19</v>
       </c>
       <c r="C1661" s="78" t="str">
@@ -33997,10 +33997,10 @@
       </c>
     </row>
     <row r="1662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1662" s="1" t="s">
+      <c r="A1662" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1662" s="2" t="n">
+      <c r="B1662" s="8" t="n">
         <v>20</v>
       </c>
       <c r="C1662" s="78" t="str">
@@ -34015,10 +34015,10 @@
       </c>
     </row>
     <row r="1663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1663" s="1" t="s">
+      <c r="A1663" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1663" s="2" t="n">
+      <c r="B1663" s="8" t="n">
         <v>21</v>
       </c>
       <c r="C1663" s="78" t="str">
@@ -34033,10 +34033,10 @@
       </c>
     </row>
     <row r="1664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1664" s="1" t="s">
+      <c r="A1664" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1664" s="2" t="n">
+      <c r="B1664" s="8" t="n">
         <v>22</v>
       </c>
       <c r="C1664" s="78" t="str">
@@ -34051,10 +34051,10 @@
       </c>
     </row>
     <row r="1665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1665" s="1" t="s">
+      <c r="A1665" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1665" s="2" t="n">
+      <c r="B1665" s="8" t="n">
         <v>23</v>
       </c>
       <c r="C1665" s="78" t="str">
@@ -34069,10 +34069,10 @@
       </c>
     </row>
     <row r="1666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1666" s="1" t="s">
+      <c r="A1666" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1666" s="2" t="n">
+      <c r="B1666" s="8" t="n">
         <v>24</v>
       </c>
       <c r="C1666" s="78" t="str">
@@ -34087,10 +34087,10 @@
       </c>
     </row>
     <row r="1667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1667" s="1" t="s">
+      <c r="A1667" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1667" s="2" t="n">
+      <c r="B1667" s="8" t="n">
         <v>25</v>
       </c>
       <c r="C1667" s="78" t="str">
@@ -34105,10 +34105,10 @@
       </c>
     </row>
     <row r="1668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1668" s="1" t="s">
+      <c r="A1668" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1668" s="2" t="n">
+      <c r="B1668" s="8" t="n">
         <v>26</v>
       </c>
       <c r="C1668" s="78" t="str">
@@ -34123,10 +34123,10 @@
       </c>
     </row>
     <row r="1669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1669" s="1" t="s">
+      <c r="A1669" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="B1669" s="2" t="n">
+      <c r="B1669" s="8" t="n">
         <v>27</v>
       </c>
       <c r="C1669" s="78" t="str">
@@ -34423,231 +34423,399 @@
       </c>
     </row>
     <row r="1687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1687" s="1" t="s">
+      <c r="A1687" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1687" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C1687" s="23" t="str">
+      <c r="B1687" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="C1687" s="80" t="str">
         <f aca="false">CONCATENATE(A1687,B1687)</f>
-        <v>BJ13</v>
+        <v>BJ32</v>
+      </c>
+      <c r="D1687" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1687" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F1687" s="1" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="1688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1688" s="1" t="s">
+      <c r="A1688" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1688" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C1688" s="23" t="str">
+      <c r="B1688" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="C1688" s="80" t="str">
         <f aca="false">CONCATENATE(A1688,B1688)</f>
-        <v>BJ14</v>
+        <v>BJ33</v>
+      </c>
+      <c r="D1688" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1688" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F1688" s="1" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="1689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1689" s="1" t="s">
+      <c r="A1689" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1689" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="C1689" s="23" t="str">
+      <c r="B1689" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="C1689" s="80" t="str">
         <f aca="false">CONCATENATE(A1689,B1689)</f>
-        <v>BJ15</v>
+        <v>BJ34</v>
+      </c>
+      <c r="D1689" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1689" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F1689" s="1" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="1690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1690" s="1" t="s">
+      <c r="A1690" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1690" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="C1690" s="23" t="str">
+      <c r="B1690" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="C1690" s="80" t="str">
         <f aca="false">CONCATENATE(A1690,B1690)</f>
-        <v>BJ16</v>
+        <v>BJ35</v>
+      </c>
+      <c r="D1690" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1690" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F1690" s="1" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="1691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1691" s="1" t="s">
+      <c r="A1691" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1691" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="C1691" s="23" t="str">
+      <c r="B1691" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="C1691" s="80" t="str">
         <f aca="false">CONCATENATE(A1691,B1691)</f>
-        <v>BJ17</v>
+        <v>BJ36</v>
+      </c>
+      <c r="D1691" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1691" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F1691" s="1" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="1692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1692" s="1" t="s">
+      <c r="A1692" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1692" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="C1692" s="23" t="str">
+      <c r="B1692" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="C1692" s="80" t="str">
         <f aca="false">CONCATENATE(A1692,B1692)</f>
-        <v>BJ18</v>
+        <v>BJ37</v>
+      </c>
+      <c r="D1692" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1692" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F1692" s="1" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="1693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1693" s="1" t="s">
+      <c r="A1693" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1693" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="C1693" s="23" t="str">
+      <c r="B1693" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1693" s="80" t="str">
         <f aca="false">CONCATENATE(A1693,B1693)</f>
-        <v>BJ19</v>
+        <v>BJ38</v>
+      </c>
+      <c r="D1693" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1693" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F1693" s="1" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="1694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1694" s="1" t="s">
+      <c r="A1694" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1694" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C1694" s="23" t="str">
+      <c r="B1694" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C1694" s="80" t="str">
         <f aca="false">CONCATENATE(A1694,B1694)</f>
-        <v>BJ20</v>
+        <v>BJ39</v>
+      </c>
+      <c r="D1694" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1694" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F1694" s="1" t="s">
+        <v>1091</v>
       </c>
     </row>
     <row r="1695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1695" s="1" t="s">
+      <c r="A1695" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1695" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C1695" s="23" t="str">
+      <c r="B1695" s="8" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C1695" s="80" t="str">
         <f aca="false">CONCATENATE(A1695,B1695)</f>
-        <v>BJ21</v>
+        <v>BJ39b</v>
+      </c>
+      <c r="D1695" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1695" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F1695" s="1" t="s">
+        <v>1191</v>
       </c>
     </row>
     <row r="1696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1696" s="1" t="s">
+      <c r="A1696" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1696" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="C1696" s="23" t="str">
+      <c r="B1696" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="C1696" s="80" t="str">
         <f aca="false">CONCATENATE(A1696,B1696)</f>
-        <v>BJ22</v>
+        <v>BJ40</v>
+      </c>
+      <c r="D1696" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1696" s="1" t="s">
+        <v>1122</v>
       </c>
     </row>
     <row r="1697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1697" s="1" t="s">
+      <c r="A1697" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1697" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="C1697" s="23" t="str">
+      <c r="B1697" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="C1697" s="80" t="str">
         <f aca="false">CONCATENATE(A1697,B1697)</f>
-        <v>BJ23</v>
+        <v>BJ41</v>
+      </c>
+      <c r="D1697" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1697" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F1697" s="1" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="1698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1698" s="1" t="s">
+      <c r="A1698" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1698" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="C1698" s="23" t="str">
+      <c r="B1698" s="8" t="n">
+        <v>42</v>
+      </c>
+      <c r="C1698" s="80" t="str">
         <f aca="false">CONCATENATE(A1698,B1698)</f>
-        <v>BJ24</v>
+        <v>BJ42</v>
+      </c>
+      <c r="D1698" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1698" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F1698" s="1" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="1699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1699" s="1" t="s">
+      <c r="A1699" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1699" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="C1699" s="23" t="str">
+      <c r="B1699" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="C1699" s="80" t="str">
         <f aca="false">CONCATENATE(A1699,B1699)</f>
-        <v>BJ25</v>
+        <v>BJ43</v>
+      </c>
+      <c r="D1699" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1699" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F1699" s="1" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="1700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1700" s="1" t="s">
+      <c r="A1700" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1700" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="C1700" s="23" t="str">
+      <c r="B1700" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="C1700" s="80" t="str">
         <f aca="false">CONCATENATE(A1700,B1700)</f>
-        <v>BJ26</v>
+        <v>BJ44</v>
+      </c>
+      <c r="D1700" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1700" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F1700" s="1" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="1701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1701" s="1" t="s">
+      <c r="A1701" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1701" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="C1701" s="23" t="str">
+      <c r="B1701" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="C1701" s="80" t="str">
         <f aca="false">CONCATENATE(A1701,B1701)</f>
-        <v>BJ27</v>
+        <v>BJ45</v>
+      </c>
+      <c r="D1701" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1701" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F1701" s="1" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="1702" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1702" s="1" t="s">
+      <c r="A1702" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1702" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="C1702" s="23" t="str">
+      <c r="B1702" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="C1702" s="80" t="str">
         <f aca="false">CONCATENATE(A1702,B1702)</f>
-        <v>BJ28</v>
+        <v>BJ46</v>
+      </c>
+      <c r="D1702" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1702" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F1702" s="1" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="1703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1703" s="1" t="s">
+      <c r="A1703" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1703" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="C1703" s="23" t="str">
+      <c r="B1703" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="C1703" s="80" t="str">
         <f aca="false">CONCATENATE(A1703,B1703)</f>
-        <v>BJ29</v>
+        <v>BJ47</v>
+      </c>
+      <c r="D1703" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1703" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F1703" s="1" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="1704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1704" s="1" t="s">
+      <c r="A1704" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1704" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="C1704" s="23" t="str">
+      <c r="B1704" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="C1704" s="80" t="str">
         <f aca="false">CONCATENATE(A1704,B1704)</f>
-        <v>BJ30</v>
+        <v>BJ48</v>
+      </c>
+      <c r="D1704" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1704" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F1704" s="1" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="1705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1705" s="1" t="s">
+      <c r="A1705" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="B1705" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="C1705" s="23" t="str">
+      <c r="B1705" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="C1705" s="80" t="str">
         <f aca="false">CONCATENATE(A1705,B1705)</f>
-        <v>BJ31</v>
+        <v>BJ49</v>
+      </c>
+      <c r="D1705" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1705" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F1705" s="1" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="1706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34655,20 +34823,20 @@
         <v>1185</v>
       </c>
       <c r="B1706" s="8" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C1706" s="80" t="str">
         <f aca="false">CONCATENATE(A1706,B1706)</f>
-        <v>BJ32</v>
+        <v>BJ50</v>
       </c>
       <c r="D1706" s="1" t="n">
         <v>10</v>
       </c>
       <c r="E1706" s="3" t="s">
-        <v>1190</v>
+        <v>1211</v>
       </c>
       <c r="F1706" s="1" t="s">
-        <v>1191</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="1707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -34676,395 +34844,314 @@
         <v>1185</v>
       </c>
       <c r="B1707" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="C1707" s="80" t="str">
+        <v>51</v>
+      </c>
+      <c r="C1707" s="81" t="str">
         <f aca="false">CONCATENATE(A1707,B1707)</f>
-        <v>BJ33</v>
-      </c>
-      <c r="D1707" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1707" s="3" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F1707" s="1" t="s">
-        <v>1191</v>
+        <v>BJ51</v>
       </c>
     </row>
     <row r="1708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1708" s="7" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="B1708" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="C1708" s="80" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1708" s="56" t="str">
         <f aca="false">CONCATENATE(A1708,B1708)</f>
-        <v>BJ34</v>
+        <v>BK1</v>
       </c>
       <c r="D1708" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1708" s="3" t="s">
-        <v>1193</v>
+        <v>11</v>
       </c>
       <c r="F1708" s="1" t="s">
-        <v>1191</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1709" s="7" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="B1709" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="C1709" s="80" t="str">
+        <v>2</v>
+      </c>
+      <c r="C1709" s="23" t="str">
         <f aca="false">CONCATENATE(A1709,B1709)</f>
-        <v>BJ35</v>
-      </c>
-      <c r="D1709" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1709" s="3" t="s">
-        <v>1194</v>
-      </c>
-      <c r="F1709" s="1" t="s">
-        <v>1191</v>
+        <v>BK2</v>
       </c>
     </row>
     <row r="1710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1710" s="7" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="B1710" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="C1710" s="80" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1710" s="23" t="str">
         <f aca="false">CONCATENATE(A1710,B1710)</f>
-        <v>BJ36</v>
-      </c>
-      <c r="D1710" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1710" s="3" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F1710" s="1" t="s">
-        <v>1191</v>
+        <v>BK3</v>
       </c>
     </row>
     <row r="1711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1711" s="7" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="B1711" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="C1711" s="80" t="str">
+        <v>4</v>
+      </c>
+      <c r="C1711" s="23" t="str">
         <f aca="false">CONCATENATE(A1711,B1711)</f>
-        <v>BJ37</v>
-      </c>
-      <c r="D1711" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1711" s="3" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F1711" s="1" t="s">
-        <v>1191</v>
+        <v>BK4</v>
       </c>
     </row>
     <row r="1712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1712" s="7" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="B1712" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="C1712" s="80" t="str">
+        <v>5</v>
+      </c>
+      <c r="C1712" s="23" t="str">
         <f aca="false">CONCATENATE(A1712,B1712)</f>
-        <v>BJ38</v>
-      </c>
-      <c r="D1712" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1712" s="3" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F1712" s="1" t="s">
-        <v>1191</v>
+        <v>BK5</v>
       </c>
     </row>
     <row r="1713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1713" s="7" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="B1713" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="C1713" s="80" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1713" s="23" t="str">
         <f aca="false">CONCATENATE(A1713,B1713)</f>
-        <v>BJ39</v>
-      </c>
-      <c r="D1713" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1713" s="3" t="s">
-        <v>1198</v>
-      </c>
-      <c r="F1713" s="1" t="s">
-        <v>1091</v>
+        <v>BK6</v>
       </c>
     </row>
     <row r="1714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1714" s="7" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1714" s="8" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C1714" s="80" t="str">
+        <v>1212</v>
+      </c>
+      <c r="B1714" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C1714" s="56" t="str">
         <f aca="false">CONCATENATE(A1714,B1714)</f>
-        <v>BJ39b</v>
+        <v>BK7</v>
       </c>
       <c r="D1714" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1714" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="1715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1715" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1715" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="C1715" s="56" t="str">
+        <f aca="false">CONCATENATE(A1715,B1715)</f>
+        <v>BK8</v>
+      </c>
+      <c r="D1715" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1715" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1716" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1716" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C1716" s="56" t="str">
+        <f aca="false">CONCATENATE(A1716,B1716)</f>
+        <v>BK9</v>
+      </c>
+      <c r="D1716" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1716" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F1716" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1717" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1717" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E1714" s="3" t="s">
-        <v>1200</v>
-      </c>
-      <c r="F1714" s="1" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="1715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1715" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1715" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="C1715" s="80" t="str">
-        <f aca="false">CONCATENATE(A1715,B1715)</f>
-        <v>BJ40</v>
-      </c>
-      <c r="D1715" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F1715" s="1" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="1716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1716" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1716" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="C1716" s="80" t="str">
-        <f aca="false">CONCATENATE(A1716,B1716)</f>
-        <v>BJ41</v>
-      </c>
-      <c r="D1716" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1716" s="3" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F1716" s="1" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="1717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1717" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1717" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="C1717" s="80" t="str">
+      <c r="C1717" s="56" t="str">
         <f aca="false">CONCATENATE(A1717,B1717)</f>
-        <v>BJ42</v>
+        <v>BK10</v>
       </c>
       <c r="D1717" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1717" s="3" t="s">
-        <v>1203</v>
+        <v>11</v>
       </c>
       <c r="F1717" s="1" t="s">
-        <v>1202</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1718" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1718" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1718" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="C1718" s="80" t="str">
+      <c r="A1718" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1718" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C1718" s="56" t="str">
         <f aca="false">CONCATENATE(A1718,B1718)</f>
-        <v>BJ43</v>
+        <v>BK11</v>
       </c>
       <c r="D1718" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1718" s="3" t="s">
-        <v>1204</v>
+        <v>11</v>
       </c>
       <c r="F1718" s="1" t="s">
-        <v>1202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1719" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1719" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1719" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="C1719" s="80" t="str">
+      <c r="A1719" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1719" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1719" s="56" t="str">
         <f aca="false">CONCATENATE(A1719,B1719)</f>
-        <v>BJ44</v>
+        <v>BK12</v>
       </c>
       <c r="D1719" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1719" s="3" t="s">
-        <v>1205</v>
+        <v>11</v>
       </c>
       <c r="F1719" s="1" t="s">
-        <v>1202</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1720" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1720" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1720" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="C1720" s="80" t="str">
+      <c r="A1720" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1720" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1720" s="56" t="str">
         <f aca="false">CONCATENATE(A1720,B1720)</f>
-        <v>BJ45</v>
+        <v>BK13</v>
       </c>
       <c r="D1720" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1720" s="3" t="s">
-        <v>1206</v>
+        <v>1214</v>
       </c>
       <c r="F1720" s="1" t="s">
-        <v>1202</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1721" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1721" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1721" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="C1721" s="80" t="str">
+      <c r="A1721" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1721" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1721" s="56" t="str">
         <f aca="false">CONCATENATE(A1721,B1721)</f>
-        <v>BJ46</v>
+        <v>BK14</v>
       </c>
       <c r="D1721" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1721" s="3" t="s">
-        <v>1207</v>
+        <v>11</v>
       </c>
       <c r="F1721" s="1" t="s">
-        <v>1202</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1722" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1722" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1722" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="C1722" s="80" t="str">
+      <c r="A1722" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1722" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1722" s="56" t="str">
         <f aca="false">CONCATENATE(A1722,B1722)</f>
-        <v>BJ47</v>
+        <v>BK15</v>
       </c>
       <c r="D1722" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1722" s="3" t="s">
-        <v>1208</v>
+        <v>11</v>
       </c>
       <c r="F1722" s="1" t="s">
-        <v>1202</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1723" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1723" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1723" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="C1723" s="80" t="str">
+      <c r="A1723" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1723" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1723" s="56" t="str">
         <f aca="false">CONCATENATE(A1723,B1723)</f>
-        <v>BJ48</v>
+        <v>BK16</v>
       </c>
       <c r="D1723" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1723" s="3" t="s">
-        <v>1209</v>
+        <v>11</v>
       </c>
       <c r="F1723" s="1" t="s">
-        <v>1202</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1724" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1724" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1724" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="C1724" s="80" t="str">
+      <c r="A1724" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1724" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1724" s="56" t="str">
         <f aca="false">CONCATENATE(A1724,B1724)</f>
-        <v>BJ49</v>
+        <v>BK17</v>
       </c>
       <c r="D1724" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1724" s="3" t="s">
-        <v>1210</v>
+        <v>1215</v>
       </c>
       <c r="F1724" s="1" t="s">
-        <v>1202</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1725" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1725" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B1725" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="C1725" s="80" t="str">
+      <c r="A1725" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B1725" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C1725" s="56" t="str">
         <f aca="false">CONCATENATE(A1725,B1725)</f>
-        <v>BJ50</v>
+        <v>BK18</v>
       </c>
       <c r="D1725" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E1725" s="3" t="s">
-        <v>1211</v>
+        <v>11</v>
       </c>
       <c r="F1725" s="1" t="s">
-        <v>1202</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1726" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35072,29 +35159,35 @@
         <v>1212</v>
       </c>
       <c r="B1726" s="8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C1726" s="56" t="str">
         <f aca="false">CONCATENATE(A1726,B1726)</f>
-        <v>BK1</v>
+        <v>BK19</v>
       </c>
       <c r="D1726" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1726" s="1" t="s">
-        <v>274</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1727" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1727" s="1" t="s">
+      <c r="A1727" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="B1727" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C1727" s="23" t="str">
+      <c r="B1727" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="C1727" s="56" t="str">
         <f aca="false">CONCATENATE(A1727,B1727)</f>
-        <v>BK2</v>
+        <v>BK20</v>
+      </c>
+      <c r="D1727" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1727" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="1728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35102,47 +35195,74 @@
         <v>1212</v>
       </c>
       <c r="B1728" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C1728" s="23" t="str">
+        <v>21</v>
+      </c>
+      <c r="C1728" s="56" t="str">
         <f aca="false">CONCATENATE(A1728,B1728)</f>
-        <v>BK3</v>
+        <v>BK21</v>
+      </c>
+      <c r="D1728" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1728" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F1728" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1729" s="1" t="s">
+      <c r="A1729" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="B1729" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C1729" s="23" t="str">
+      <c r="B1729" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="C1729" s="56" t="str">
         <f aca="false">CONCATENATE(A1729,B1729)</f>
-        <v>BK4</v>
+        <v>BK22</v>
+      </c>
+      <c r="D1729" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1729" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1730" s="1" t="s">
+      <c r="A1730" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="B1730" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C1730" s="23" t="str">
+      <c r="B1730" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="C1730" s="56" t="str">
         <f aca="false">CONCATENATE(A1730,B1730)</f>
-        <v>BK5</v>
+        <v>BK23</v>
+      </c>
+      <c r="D1730" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1730" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="1731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1731" s="1" t="s">
+      <c r="A1731" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="B1731" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C1731" s="23" t="str">
+      <c r="B1731" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="C1731" s="56" t="str">
         <f aca="false">CONCATENATE(A1731,B1731)</f>
-        <v>BK6</v>
+        <v>BK24</v>
+      </c>
+      <c r="D1731" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1731" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="1732" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35150,17 +35270,20 @@
         <v>1212</v>
       </c>
       <c r="B1732" s="8" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C1732" s="56" t="str">
         <f aca="false">CONCATENATE(A1732,B1732)</f>
-        <v>BK7</v>
+        <v>BK25</v>
       </c>
       <c r="D1732" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E1732" s="3" t="s">
+        <v>1217</v>
+      </c>
       <c r="F1732" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1733" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35168,17 +35291,17 @@
         <v>1212</v>
       </c>
       <c r="B1733" s="8" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C1733" s="56" t="str">
         <f aca="false">CONCATENATE(A1733,B1733)</f>
-        <v>BK8</v>
+        <v>BK26</v>
       </c>
       <c r="D1733" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1733" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35186,20 +35309,17 @@
         <v>1212</v>
       </c>
       <c r="B1734" s="8" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C1734" s="56" t="str">
         <f aca="false">CONCATENATE(A1734,B1734)</f>
-        <v>BK9</v>
+        <v>BK27</v>
       </c>
       <c r="D1734" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E1734" s="3" t="s">
-        <v>1213</v>
-      </c>
       <c r="F1734" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35207,17 +35327,17 @@
         <v>1212</v>
       </c>
       <c r="B1735" s="8" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C1735" s="56" t="str">
         <f aca="false">CONCATENATE(A1735,B1735)</f>
-        <v>BK10</v>
+        <v>BK28</v>
       </c>
       <c r="D1735" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1735" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35225,17 +35345,20 @@
         <v>1212</v>
       </c>
       <c r="B1736" s="8" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C1736" s="56" t="str">
         <f aca="false">CONCATENATE(A1736,B1736)</f>
-        <v>BK11</v>
+        <v>BK29</v>
       </c>
       <c r="D1736" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E1736" s="3" t="s">
+        <v>1218</v>
+      </c>
       <c r="F1736" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1737" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35243,17 +35366,17 @@
         <v>1212</v>
       </c>
       <c r="B1737" s="8" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C1737" s="56" t="str">
         <f aca="false">CONCATENATE(A1737,B1737)</f>
-        <v>BK12</v>
+        <v>BK30</v>
       </c>
       <c r="D1737" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1737" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1738" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35261,20 +35384,17 @@
         <v>1212</v>
       </c>
       <c r="B1738" s="8" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C1738" s="56" t="str">
         <f aca="false">CONCATENATE(A1738,B1738)</f>
-        <v>BK13</v>
+        <v>BK31</v>
       </c>
       <c r="D1738" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E1738" s="3" t="s">
-        <v>1214</v>
-      </c>
       <c r="F1738" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1739" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35282,17 +35402,17 @@
         <v>1212</v>
       </c>
       <c r="B1739" s="8" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C1739" s="56" t="str">
         <f aca="false">CONCATENATE(A1739,B1739)</f>
-        <v>BK14</v>
+        <v>BK32</v>
       </c>
       <c r="D1739" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1739" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1740" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35300,17 +35420,20 @@
         <v>1212</v>
       </c>
       <c r="B1740" s="8" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C1740" s="56" t="str">
         <f aca="false">CONCATENATE(A1740,B1740)</f>
-        <v>BK15</v>
+        <v>BK33</v>
       </c>
       <c r="D1740" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E1740" s="3" t="s">
+        <v>1219</v>
+      </c>
       <c r="F1740" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1741" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35318,17 +35441,17 @@
         <v>1212</v>
       </c>
       <c r="B1741" s="8" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C1741" s="56" t="str">
         <f aca="false">CONCATENATE(A1741,B1741)</f>
-        <v>BK16</v>
+        <v>BK34</v>
       </c>
       <c r="D1741" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1741" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1742" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35336,20 +35459,17 @@
         <v>1212</v>
       </c>
       <c r="B1742" s="8" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C1742" s="56" t="str">
         <f aca="false">CONCATENATE(A1742,B1742)</f>
-        <v>BK17</v>
+        <v>BK35</v>
       </c>
       <c r="D1742" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E1742" s="3" t="s">
-        <v>1215</v>
-      </c>
       <c r="F1742" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35357,17 +35477,17 @@
         <v>1212</v>
       </c>
       <c r="B1743" s="8" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C1743" s="56" t="str">
         <f aca="false">CONCATENATE(A1743,B1743)</f>
-        <v>BK18</v>
+        <v>BK36</v>
       </c>
       <c r="D1743" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1743" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1744" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35375,17 +35495,20 @@
         <v>1212</v>
       </c>
       <c r="B1744" s="8" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C1744" s="56" t="str">
         <f aca="false">CONCATENATE(A1744,B1744)</f>
-        <v>BK19</v>
+        <v>BK37</v>
       </c>
       <c r="D1744" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E1744" s="3" t="s">
+        <v>1220</v>
+      </c>
       <c r="F1744" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1745" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35393,17 +35516,17 @@
         <v>1212</v>
       </c>
       <c r="B1745" s="8" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C1745" s="56" t="str">
         <f aca="false">CONCATENATE(A1745,B1745)</f>
-        <v>BK20</v>
+        <v>BK38</v>
       </c>
       <c r="D1745" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1745" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1746" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35411,20 +35534,17 @@
         <v>1212</v>
       </c>
       <c r="B1746" s="8" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C1746" s="56" t="str">
         <f aca="false">CONCATENATE(A1746,B1746)</f>
-        <v>BK21</v>
+        <v>BK39</v>
       </c>
       <c r="D1746" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E1746" s="3" t="s">
-        <v>1216</v>
-      </c>
       <c r="F1746" s="1" t="s">
-        <v>13</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1747" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35432,11 +35552,11 @@
         <v>1212</v>
       </c>
       <c r="B1747" s="8" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C1747" s="56" t="str">
         <f aca="false">CONCATENATE(A1747,B1747)</f>
-        <v>BK22</v>
+        <v>BK40</v>
       </c>
       <c r="D1747" s="1" t="n">
         <v>11</v>
@@ -35450,17 +35570,17 @@
         <v>1212</v>
       </c>
       <c r="B1748" s="8" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C1748" s="56" t="str">
         <f aca="false">CONCATENATE(A1748,B1748)</f>
-        <v>BK23</v>
+        <v>BK41</v>
       </c>
       <c r="D1748" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1748" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1749" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35468,17 +35588,17 @@
         <v>1212</v>
       </c>
       <c r="B1749" s="8" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C1749" s="56" t="str">
         <f aca="false">CONCATENATE(A1749,B1749)</f>
-        <v>BK24</v>
+        <v>BK42</v>
       </c>
       <c r="D1749" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1749" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1750" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35486,17 +35606,14 @@
         <v>1212</v>
       </c>
       <c r="B1750" s="8" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C1750" s="56" t="str">
         <f aca="false">CONCATENATE(A1750,B1750)</f>
-        <v>BK25</v>
+        <v>BK43</v>
       </c>
       <c r="D1750" s="1" t="n">
         <v>11</v>
-      </c>
-      <c r="E1750" s="3" t="s">
-        <v>1217</v>
       </c>
       <c r="F1750" s="1" t="s">
         <v>13</v>
@@ -35507,17 +35624,17 @@
         <v>1212</v>
       </c>
       <c r="B1751" s="8" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C1751" s="56" t="str">
         <f aca="false">CONCATENATE(A1751,B1751)</f>
-        <v>BK26</v>
+        <v>BK44</v>
       </c>
       <c r="D1751" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1751" s="1" t="s">
-        <v>13</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35525,17 +35642,11 @@
         <v>1212</v>
       </c>
       <c r="B1752" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="C1752" s="56" t="str">
+        <v>45</v>
+      </c>
+      <c r="C1752" s="23" t="str">
         <f aca="false">CONCATENATE(A1752,B1752)</f>
-        <v>BK27</v>
-      </c>
-      <c r="D1752" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1752" s="1" t="s">
-        <v>33</v>
+        <v>BK45</v>
       </c>
     </row>
     <row r="1753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35543,17 +35654,11 @@
         <v>1212</v>
       </c>
       <c r="B1753" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C1753" s="56" t="str">
+        <v>46</v>
+      </c>
+      <c r="C1753" s="23" t="str">
         <f aca="false">CONCATENATE(A1753,B1753)</f>
-        <v>BK28</v>
-      </c>
-      <c r="D1753" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1753" s="1" t="s">
-        <v>8</v>
+        <v>BK46</v>
       </c>
     </row>
     <row r="1754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35561,20 +35666,11 @@
         <v>1212</v>
       </c>
       <c r="B1754" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="C1754" s="56" t="str">
+        <v>47</v>
+      </c>
+      <c r="C1754" s="23" t="str">
         <f aca="false">CONCATENATE(A1754,B1754)</f>
-        <v>BK29</v>
-      </c>
-      <c r="D1754" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E1754" s="3" t="s">
-        <v>1218</v>
-      </c>
-      <c r="F1754" s="1" t="s">
-        <v>13</v>
+        <v>BK47</v>
       </c>
     </row>
     <row r="1755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35582,17 +35678,11 @@
         <v>1212</v>
       </c>
       <c r="B1755" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="C1755" s="56" t="str">
+        <v>48</v>
+      </c>
+      <c r="C1755" s="23" t="str">
         <f aca="false">CONCATENATE(A1755,B1755)</f>
-        <v>BK30</v>
-      </c>
-      <c r="D1755" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1755" s="1" t="s">
-        <v>13</v>
+        <v>BK48</v>
       </c>
     </row>
     <row r="1756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35600,17 +35690,11 @@
         <v>1212</v>
       </c>
       <c r="B1756" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="C1756" s="56" t="str">
+        <v>49</v>
+      </c>
+      <c r="C1756" s="23" t="str">
         <f aca="false">CONCATENATE(A1756,B1756)</f>
-        <v>BK31</v>
-      </c>
-      <c r="D1756" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1756" s="1" t="s">
-        <v>33</v>
+        <v>BK49</v>
       </c>
     </row>
     <row r="1757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35618,17 +35702,11 @@
         <v>1212</v>
       </c>
       <c r="B1757" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="C1757" s="56" t="str">
+        <v>50</v>
+      </c>
+      <c r="C1757" s="23" t="str">
         <f aca="false">CONCATENATE(A1757,B1757)</f>
-        <v>BK32</v>
-      </c>
-      <c r="D1757" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1757" s="1" t="s">
-        <v>8</v>
+        <v>BK50</v>
       </c>
     </row>
     <row r="1758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35636,20 +35714,11 @@
         <v>1212</v>
       </c>
       <c r="B1758" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="C1758" s="56" t="str">
+        <v>51</v>
+      </c>
+      <c r="C1758" s="23" t="str">
         <f aca="false">CONCATENATE(A1758,B1758)</f>
-        <v>BK33</v>
-      </c>
-      <c r="D1758" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E1758" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="F1758" s="1" t="s">
-        <v>13</v>
+        <v>BK51</v>
       </c>
     </row>
     <row r="1759" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35657,17 +35726,11 @@
         <v>1212</v>
       </c>
       <c r="B1759" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="C1759" s="56" t="str">
+        <v>52</v>
+      </c>
+      <c r="C1759" s="23" t="str">
         <f aca="false">CONCATENATE(A1759,B1759)</f>
-        <v>BK34</v>
-      </c>
-      <c r="D1759" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1759" s="1" t="s">
-        <v>13</v>
+        <v>BK52</v>
       </c>
     </row>
     <row r="1760" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35675,17 +35738,17 @@
         <v>1212</v>
       </c>
       <c r="B1760" s="8" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C1760" s="56" t="str">
         <f aca="false">CONCATENATE(A1760,B1760)</f>
-        <v>BK35</v>
+        <v>BK53</v>
       </c>
       <c r="D1760" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1760" s="1" t="s">
-        <v>33</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1761" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35693,17 +35756,20 @@
         <v>1212</v>
       </c>
       <c r="B1761" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="C1761" s="56" t="str">
+        <v>54</v>
+      </c>
+      <c r="C1761" s="82" t="str">
         <f aca="false">CONCATENATE(A1761,B1761)</f>
-        <v>BK36</v>
+        <v>BK54</v>
       </c>
       <c r="D1761" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E1761" s="3" t="s">
+        <v>1221</v>
+      </c>
       <c r="F1761" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1762" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35711,20 +35777,17 @@
         <v>1212</v>
       </c>
       <c r="B1762" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="C1762" s="56" t="str">
+        <v>55</v>
+      </c>
+      <c r="C1762" s="82" t="str">
         <f aca="false">CONCATENATE(A1762,B1762)</f>
-        <v>BK37</v>
+        <v>BK55</v>
       </c>
       <c r="D1762" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="E1762" s="3" t="s">
-        <v>1220</v>
-      </c>
       <c r="F1762" s="1" t="s">
-        <v>13</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="1763" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35732,17 +35795,17 @@
         <v>1212</v>
       </c>
       <c r="B1763" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="C1763" s="56" t="str">
+        <v>56</v>
+      </c>
+      <c r="C1763" s="82" t="str">
         <f aca="false">CONCATENATE(A1763,B1763)</f>
-        <v>BK38</v>
+        <v>BK56</v>
       </c>
       <c r="D1763" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1763" s="1" t="s">
-        <v>13</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="1764" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35750,17 +35813,20 @@
         <v>1212</v>
       </c>
       <c r="B1764" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="C1764" s="56" t="str">
+        <v>57</v>
+      </c>
+      <c r="C1764" s="82" t="str">
         <f aca="false">CONCATENATE(A1764,B1764)</f>
-        <v>BK39</v>
+        <v>BK57</v>
       </c>
       <c r="D1764" s="1" t="n">
         <v>11</v>
       </c>
+      <c r="E1764" s="3" t="s">
+        <v>1224</v>
+      </c>
       <c r="F1764" s="1" t="s">
-        <v>274</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1765" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35768,11 +35834,11 @@
         <v>1212</v>
       </c>
       <c r="B1765" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="C1765" s="56" t="str">
+        <v>58</v>
+      </c>
+      <c r="C1765" s="82" t="str">
         <f aca="false">CONCATENATE(A1765,B1765)</f>
-        <v>BK40</v>
+        <v>BK58</v>
       </c>
       <c r="D1765" s="1" t="n">
         <v>11</v>
@@ -35786,11 +35852,11 @@
         <v>1212</v>
       </c>
       <c r="B1766" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="C1766" s="56" t="str">
+        <v>59</v>
+      </c>
+      <c r="C1766" s="82" t="str">
         <f aca="false">CONCATENATE(A1766,B1766)</f>
-        <v>BK41</v>
+        <v>BK59</v>
       </c>
       <c r="D1766" s="1" t="n">
         <v>11</v>
@@ -35804,14 +35870,17 @@
         <v>1212</v>
       </c>
       <c r="B1767" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="C1767" s="56" t="str">
+        <v>60</v>
+      </c>
+      <c r="C1767" s="82" t="str">
         <f aca="false">CONCATENATE(A1767,B1767)</f>
-        <v>BK42</v>
+        <v>BK60</v>
       </c>
       <c r="D1767" s="1" t="n">
         <v>11</v>
+      </c>
+      <c r="E1767" s="3" t="s">
+        <v>1225</v>
       </c>
       <c r="F1767" s="1" t="s">
         <v>13</v>
@@ -35822,17 +35891,17 @@
         <v>1212</v>
       </c>
       <c r="B1768" s="8" t="n">
-        <v>43</v>
-      </c>
-      <c r="C1768" s="56" t="str">
+        <v>61</v>
+      </c>
+      <c r="C1768" s="82" t="str">
         <f aca="false">CONCATENATE(A1768,B1768)</f>
-        <v>BK43</v>
+        <v>BK61</v>
       </c>
       <c r="D1768" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1768" s="1" t="s">
-        <v>13</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1769" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35840,17 +35909,17 @@
         <v>1212</v>
       </c>
       <c r="B1769" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="C1769" s="56" t="str">
+        <v>62</v>
+      </c>
+      <c r="C1769" s="82" t="str">
         <f aca="false">CONCATENATE(A1769,B1769)</f>
-        <v>BK44</v>
+        <v>BK62</v>
       </c>
       <c r="D1769" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1769" s="1" t="s">
-        <v>274</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1770" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35858,11 +35927,20 @@
         <v>1212</v>
       </c>
       <c r="B1770" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="C1770" s="23" t="str">
+        <v>63</v>
+      </c>
+      <c r="C1770" s="82" t="str">
         <f aca="false">CONCATENATE(A1770,B1770)</f>
-        <v>BK45</v>
+        <v>BK63</v>
+      </c>
+      <c r="D1770" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1770" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F1770" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1771" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35870,11 +35948,17 @@
         <v>1212</v>
       </c>
       <c r="B1771" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="C1771" s="23" t="str">
+        <v>64</v>
+      </c>
+      <c r="C1771" s="82" t="str">
         <f aca="false">CONCATENATE(A1771,B1771)</f>
-        <v>BK46</v>
+        <v>BK64</v>
+      </c>
+      <c r="D1771" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1771" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1772" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35882,11 +35966,17 @@
         <v>1212</v>
       </c>
       <c r="B1772" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="C1772" s="23" t="str">
+        <v>65</v>
+      </c>
+      <c r="C1772" s="82" t="str">
         <f aca="false">CONCATENATE(A1772,B1772)</f>
-        <v>BK47</v>
+        <v>BK65</v>
+      </c>
+      <c r="D1772" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1772" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1773" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35894,11 +35984,20 @@
         <v>1212</v>
       </c>
       <c r="B1773" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="C1773" s="23" t="str">
+        <v>66</v>
+      </c>
+      <c r="C1773" s="82" t="str">
         <f aca="false">CONCATENATE(A1773,B1773)</f>
-        <v>BK48</v>
+        <v>BK66</v>
+      </c>
+      <c r="D1773" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1773" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F1773" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1774" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35906,11 +36005,17 @@
         <v>1212</v>
       </c>
       <c r="B1774" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="C1774" s="23" t="str">
+        <v>67</v>
+      </c>
+      <c r="C1774" s="82" t="str">
         <f aca="false">CONCATENATE(A1774,B1774)</f>
-        <v>BK49</v>
+        <v>BK67</v>
+      </c>
+      <c r="D1774" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1774" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="1775" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35918,11 +36023,17 @@
         <v>1212</v>
       </c>
       <c r="B1775" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="C1775" s="23" t="str">
+        <v>68</v>
+      </c>
+      <c r="C1775" s="82" t="str">
         <f aca="false">CONCATENATE(A1775,B1775)</f>
-        <v>BK50</v>
+        <v>BK68</v>
+      </c>
+      <c r="D1775" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1775" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="1776" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35930,11 +36041,20 @@
         <v>1212</v>
       </c>
       <c r="B1776" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="C1776" s="23" t="str">
+        <v>69</v>
+      </c>
+      <c r="C1776" s="82" t="str">
         <f aca="false">CONCATENATE(A1776,B1776)</f>
-        <v>BK51</v>
+        <v>BK69</v>
+      </c>
+      <c r="D1776" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1776" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F1776" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1777" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35942,11 +36062,17 @@
         <v>1212</v>
       </c>
       <c r="B1777" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="C1777" s="23" t="str">
+        <v>70</v>
+      </c>
+      <c r="C1777" s="82" t="str">
         <f aca="false">CONCATENATE(A1777,B1777)</f>
-        <v>BK52</v>
+        <v>BK70</v>
+      </c>
+      <c r="D1777" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1777" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1778" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35954,17 +36080,17 @@
         <v>1212</v>
       </c>
       <c r="B1778" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="C1778" s="56" t="str">
+        <v>71</v>
+      </c>
+      <c r="C1778" s="82" t="str">
         <f aca="false">CONCATENATE(A1778,B1778)</f>
-        <v>BK53</v>
+        <v>BK71</v>
       </c>
       <c r="D1778" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1778" s="1" t="s">
-        <v>274</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1779" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35972,17 +36098,17 @@
         <v>1212</v>
       </c>
       <c r="B1779" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="C1779" s="81" t="str">
+        <v>72</v>
+      </c>
+      <c r="C1779" s="82" t="str">
         <f aca="false">CONCATENATE(A1779,B1779)</f>
-        <v>BK54</v>
+        <v>BK72</v>
       </c>
       <c r="D1779" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E1779" s="3" t="s">
-        <v>1221</v>
+        <v>1229</v>
       </c>
       <c r="F1779" s="1" t="s">
         <v>13</v>
@@ -35993,17 +36119,17 @@
         <v>1212</v>
       </c>
       <c r="B1780" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="C1780" s="81" t="str">
+        <v>73</v>
+      </c>
+      <c r="C1780" s="82" t="str">
         <f aca="false">CONCATENATE(A1780,B1780)</f>
-        <v>BK55</v>
+        <v>BK73</v>
       </c>
       <c r="D1780" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1780" s="1" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="1781" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36011,17 +36137,17 @@
         <v>1212</v>
       </c>
       <c r="B1781" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="C1781" s="81" t="str">
+        <v>74</v>
+      </c>
+      <c r="C1781" s="82" t="str">
         <f aca="false">CONCATENATE(A1781,B1781)</f>
-        <v>BK56</v>
+        <v>BK74</v>
       </c>
       <c r="D1781" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1781" s="1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="1782" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36029,17 +36155,17 @@
         <v>1212</v>
       </c>
       <c r="B1782" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="C1782" s="81" t="str">
+        <v>75</v>
+      </c>
+      <c r="C1782" s="82" t="str">
         <f aca="false">CONCATENATE(A1782,B1782)</f>
-        <v>BK57</v>
+        <v>BK75</v>
       </c>
       <c r="D1782" s="1" t="n">
         <v>11</v>
       </c>
       <c r="E1782" s="3" t="s">
-        <v>1224</v>
+        <v>1230</v>
       </c>
       <c r="F1782" s="1" t="s">
         <v>13</v>
@@ -36050,11 +36176,11 @@
         <v>1212</v>
       </c>
       <c r="B1783" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="C1783" s="81" t="str">
+        <v>76</v>
+      </c>
+      <c r="C1783" s="82" t="str">
         <f aca="false">CONCATENATE(A1783,B1783)</f>
-        <v>BK58</v>
+        <v>BK76</v>
       </c>
       <c r="D1783" s="1" t="n">
         <v>11</v>
@@ -36068,17 +36194,17 @@
         <v>1212</v>
       </c>
       <c r="B1784" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="C1784" s="81" t="str">
+        <v>77</v>
+      </c>
+      <c r="C1784" s="80" t="str">
         <f aca="false">CONCATENATE(A1784,B1784)</f>
-        <v>BK59</v>
+        <v>BK77</v>
       </c>
       <c r="D1784" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1784" s="1" t="s">
-        <v>13</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="1785" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36086,20 +36212,17 @@
         <v>1212</v>
       </c>
       <c r="B1785" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="C1785" s="81" t="str">
+        <v>78</v>
+      </c>
+      <c r="C1785" s="80" t="str">
         <f aca="false">CONCATENATE(A1785,B1785)</f>
-        <v>BK60</v>
+        <v>BK78</v>
       </c>
       <c r="D1785" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E1785" s="3" t="s">
-        <v>1225</v>
+        <v>10</v>
       </c>
       <c r="F1785" s="1" t="s">
-        <v>13</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="1786" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36107,17 +36230,17 @@
         <v>1212</v>
       </c>
       <c r="B1786" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="C1786" s="81" t="str">
+        <v>79</v>
+      </c>
+      <c r="C1786" s="83" t="str">
         <f aca="false">CONCATENATE(A1786,B1786)</f>
-        <v>BK61</v>
+        <v>BK79</v>
       </c>
       <c r="D1786" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F1786" s="1" t="s">
-        <v>118</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1787" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36125,17 +36248,17 @@
         <v>1212</v>
       </c>
       <c r="B1787" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="C1787" s="81" t="str">
+        <v>80</v>
+      </c>
+      <c r="C1787" s="83" t="str">
         <f aca="false">CONCATENATE(A1787,B1787)</f>
-        <v>BK62</v>
+        <v>BK80</v>
       </c>
       <c r="D1787" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F1787" s="1" t="s">
-        <v>118</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1788" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36143,17 +36266,14 @@
         <v>1212</v>
       </c>
       <c r="B1788" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="C1788" s="81" t="str">
+        <v>81</v>
+      </c>
+      <c r="C1788" s="83" t="str">
         <f aca="false">CONCATENATE(A1788,B1788)</f>
-        <v>BK63</v>
+        <v>BK81</v>
       </c>
       <c r="D1788" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E1788" s="3" t="s">
-        <v>1226</v>
+        <v>7</v>
       </c>
       <c r="F1788" s="1" t="s">
         <v>13</v>
@@ -36164,17 +36284,20 @@
         <v>1212</v>
       </c>
       <c r="B1789" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="C1789" s="81" t="str">
+        <v>82</v>
+      </c>
+      <c r="C1789" s="83" t="str">
         <f aca="false">CONCATENATE(A1789,B1789)</f>
-        <v>BK64</v>
+        <v>BK82</v>
       </c>
       <c r="D1789" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="E1789" s="3" t="s">
+        <v>1231</v>
       </c>
       <c r="F1789" s="1" t="s">
-        <v>13</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1790" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36182,17 +36305,17 @@
         <v>1212</v>
       </c>
       <c r="B1790" s="8" t="n">
-        <v>65</v>
-      </c>
-      <c r="C1790" s="81" t="str">
+        <v>83</v>
+      </c>
+      <c r="C1790" s="83" t="str">
         <f aca="false">CONCATENATE(A1790,B1790)</f>
-        <v>BK65</v>
+        <v>BK83</v>
       </c>
       <c r="D1790" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F1790" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1791" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36200,20 +36323,17 @@
         <v>1212</v>
       </c>
       <c r="B1791" s="8" t="n">
-        <v>66</v>
-      </c>
-      <c r="C1791" s="81" t="str">
+        <v>84</v>
+      </c>
+      <c r="C1791" s="83" t="str">
         <f aca="false">CONCATENATE(A1791,B1791)</f>
-        <v>BK66</v>
+        <v>BK84</v>
       </c>
       <c r="D1791" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E1791" s="3" t="s">
-        <v>1227</v>
+        <v>7</v>
       </c>
       <c r="F1791" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1792" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36221,17 +36341,17 @@
         <v>1212</v>
       </c>
       <c r="B1792" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="C1792" s="81" t="str">
+        <v>85</v>
+      </c>
+      <c r="C1792" s="83" t="str">
         <f aca="false">CONCATENATE(A1792,B1792)</f>
-        <v>BK67</v>
+        <v>BK85</v>
       </c>
       <c r="D1792" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F1792" s="1" t="s">
-        <v>118</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1793" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36239,17 +36359,17 @@
         <v>1212</v>
       </c>
       <c r="B1793" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="C1793" s="81" t="str">
+        <v>86</v>
+      </c>
+      <c r="C1793" s="83" t="str">
         <f aca="false">CONCATENATE(A1793,B1793)</f>
-        <v>BK68</v>
+        <v>BK86</v>
       </c>
       <c r="D1793" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F1793" s="1" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1794" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36257,20 +36377,17 @@
         <v>1212</v>
       </c>
       <c r="B1794" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="C1794" s="81" t="str">
+        <v>87</v>
+      </c>
+      <c r="C1794" s="83" t="str">
         <f aca="false">CONCATENATE(A1794,B1794)</f>
-        <v>BK69</v>
+        <v>BK87</v>
       </c>
       <c r="D1794" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E1794" s="3" t="s">
-        <v>1228</v>
+        <v>7</v>
       </c>
       <c r="F1794" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1795" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36278,17 +36395,17 @@
         <v>1212</v>
       </c>
       <c r="B1795" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="C1795" s="81" t="str">
+        <v>88</v>
+      </c>
+      <c r="C1795" s="83" t="str">
         <f aca="false">CONCATENATE(A1795,B1795)</f>
-        <v>BK70</v>
+        <v>BK88</v>
       </c>
       <c r="D1795" s="1" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F1795" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1796" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36296,17 +36413,14 @@
         <v>1212</v>
       </c>
       <c r="B1796" s="8" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C1796" s="81" t="str">
         <f aca="false">CONCATENATE(A1796,B1796)</f>
-        <v>BK71</v>
-      </c>
-      <c r="D1796" s="1" t="n">
-        <v>11</v>
+        <v>BK89</v>
       </c>
       <c r="F1796" s="1" t="s">
-        <v>13</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="1797" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36314,17 +36428,14 @@
         <v>1212</v>
       </c>
       <c r="B1797" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="C1797" s="81" t="str">
+        <v>90</v>
+      </c>
+      <c r="C1797" s="80" t="str">
         <f aca="false">CONCATENATE(A1797,B1797)</f>
-        <v>BK72</v>
+        <v>BK90</v>
       </c>
       <c r="D1797" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E1797" s="3" t="s">
-        <v>1229</v>
+        <v>10</v>
       </c>
       <c r="F1797" s="1" t="s">
         <v>13</v>
@@ -36335,17 +36446,11 @@
         <v>1212</v>
       </c>
       <c r="B1798" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="C1798" s="81" t="str">
+        <v>91</v>
+      </c>
+      <c r="C1798" s="23" t="str">
         <f aca="false">CONCATENATE(A1798,B1798)</f>
-        <v>BK73</v>
-      </c>
-      <c r="D1798" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1798" s="1" t="s">
-        <v>1223</v>
+        <v>BK91</v>
       </c>
     </row>
     <row r="1799" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36353,17 +36458,11 @@
         <v>1212</v>
       </c>
       <c r="B1799" s="8" t="n">
-        <v>74</v>
-      </c>
-      <c r="C1799" s="81" t="str">
+        <v>92</v>
+      </c>
+      <c r="C1799" s="23" t="str">
         <f aca="false">CONCATENATE(A1799,B1799)</f>
-        <v>BK74</v>
-      </c>
-      <c r="D1799" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1799" s="1" t="s">
-        <v>1222</v>
+        <v>BK92</v>
       </c>
     </row>
     <row r="1800" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36371,20 +36470,11 @@
         <v>1212</v>
       </c>
       <c r="B1800" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="C1800" s="81" t="str">
+        <v>93</v>
+      </c>
+      <c r="C1800" s="23" t="str">
         <f aca="false">CONCATENATE(A1800,B1800)</f>
-        <v>BK75</v>
-      </c>
-      <c r="D1800" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E1800" s="3" t="s">
-        <v>1230</v>
-      </c>
-      <c r="F1800" s="1" t="s">
-        <v>13</v>
+        <v>BK93</v>
       </c>
     </row>
     <row r="1801" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36392,17 +36482,11 @@
         <v>1212</v>
       </c>
       <c r="B1801" s="8" t="n">
-        <v>76</v>
-      </c>
-      <c r="C1801" s="81" t="str">
+        <v>94</v>
+      </c>
+      <c r="C1801" s="23" t="str">
         <f aca="false">CONCATENATE(A1801,B1801)</f>
-        <v>BK76</v>
-      </c>
-      <c r="D1801" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1801" s="1" t="s">
-        <v>13</v>
+        <v>BK94</v>
       </c>
     </row>
     <row r="1802" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36410,17 +36494,11 @@
         <v>1212</v>
       </c>
       <c r="B1802" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="C1802" s="80" t="str">
+        <v>95</v>
+      </c>
+      <c r="C1802" s="23" t="str">
         <f aca="false">CONCATENATE(A1802,B1802)</f>
-        <v>BK77</v>
-      </c>
-      <c r="D1802" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F1802" s="1" t="s">
-        <v>1117</v>
+        <v>BK95</v>
       </c>
     </row>
     <row r="1803" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36428,17 +36506,11 @@
         <v>1212</v>
       </c>
       <c r="B1803" s="8" t="n">
-        <v>78</v>
-      </c>
-      <c r="C1803" s="80" t="str">
+        <v>96</v>
+      </c>
+      <c r="C1803" s="23" t="str">
         <f aca="false">CONCATENATE(A1803,B1803)</f>
-        <v>BK78</v>
-      </c>
-      <c r="D1803" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F1803" s="1" t="s">
-        <v>1117</v>
+        <v>BK96</v>
       </c>
     </row>
     <row r="1804" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36446,299 +36518,311 @@
         <v>1212</v>
       </c>
       <c r="B1804" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="C1804" s="82" t="str">
+        <v>97</v>
+      </c>
+      <c r="C1804" s="23" t="str">
         <f aca="false">CONCATENATE(A1804,B1804)</f>
-        <v>BK79</v>
-      </c>
-      <c r="D1804" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="F1804" s="1" t="s">
-        <v>13</v>
+        <v>BK97</v>
       </c>
     </row>
     <row r="1805" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1805" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1805" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="C1805" s="82" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1805" s="56" t="str">
         <f aca="false">CONCATENATE(A1805,B1805)</f>
-        <v>BK80</v>
+        <v>BL1</v>
       </c>
       <c r="D1805" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F1805" s="1" t="s">
-        <v>13</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1806" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1806" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1806" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="C1806" s="82" t="str">
+        <v>2</v>
+      </c>
+      <c r="C1806" s="56" t="str">
         <f aca="false">CONCATENATE(A1806,B1806)</f>
-        <v>BK81</v>
+        <v>BL2</v>
       </c>
       <c r="D1806" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F1806" s="1" t="s">
-        <v>13</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1807" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1807" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1807" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="C1807" s="82" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1807" s="56" t="str">
         <f aca="false">CONCATENATE(A1807,B1807)</f>
-        <v>BK82</v>
+        <v>BL3</v>
       </c>
       <c r="D1807" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E1807" s="3" t="s">
-        <v>1231</v>
+        <v>11</v>
       </c>
       <c r="F1807" s="1" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1808" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1808" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1808" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="C1808" s="82" t="str">
+        <v>4</v>
+      </c>
+      <c r="C1808" s="56" t="str">
         <f aca="false">CONCATENATE(A1808,B1808)</f>
-        <v>BK83</v>
+        <v>BL4</v>
       </c>
       <c r="D1808" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F1808" s="1" t="s">
-        <v>33</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1809" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1809" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="C1809" s="82" t="str">
+        <v>5</v>
+      </c>
+      <c r="C1809" s="56" t="str">
         <f aca="false">CONCATENATE(A1809,B1809)</f>
-        <v>BK84</v>
+        <v>BL5</v>
       </c>
       <c r="D1809" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F1809" s="1" t="s">
-        <v>33</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1810" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1810" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1810" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="C1810" s="82" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1810" s="56" t="str">
         <f aca="false">CONCATENATE(A1810,B1810)</f>
-        <v>BK85</v>
+        <v>BL6</v>
       </c>
       <c r="D1810" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F1810" s="1" t="s">
-        <v>13</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1811" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1811" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1811" s="8" t="n">
-        <v>86</v>
-      </c>
-      <c r="C1811" s="82" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1811" s="56" t="str">
         <f aca="false">CONCATENATE(A1811,B1811)</f>
-        <v>BK86</v>
+        <v>BL7</v>
       </c>
       <c r="D1811" s="1" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F1811" s="1" t="s">
-        <v>33</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1812" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1812" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1812" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="C1812" s="82" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1812" s="23" t="str">
         <f aca="false">CONCATENATE(A1812,B1812)</f>
-        <v>BK87</v>
-      </c>
-      <c r="D1812" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="F1812" s="1" t="s">
-        <v>8</v>
+        <v>BL8</v>
       </c>
     </row>
     <row r="1813" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1813" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1813" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="C1813" s="82" t="str">
+        <v>9</v>
+      </c>
+      <c r="C1813" s="23" t="str">
         <f aca="false">CONCATENATE(A1813,B1813)</f>
-        <v>BK88</v>
-      </c>
-      <c r="D1813" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="F1813" s="1" t="s">
-        <v>8</v>
+        <v>BL9</v>
       </c>
     </row>
     <row r="1814" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1814" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1814" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="C1814" s="83" t="str">
+        <v>10</v>
+      </c>
+      <c r="C1814" s="23" t="str">
         <f aca="false">CONCATENATE(A1814,B1814)</f>
-        <v>BK89</v>
-      </c>
-      <c r="F1814" s="1" t="s">
-        <v>1232</v>
+        <v>BL10</v>
       </c>
     </row>
     <row r="1815" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1815" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1815" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="C1815" s="80" t="str">
+        <v>11</v>
+      </c>
+      <c r="C1815" s="23" t="str">
         <f aca="false">CONCATENATE(A1815,B1815)</f>
-        <v>BK90</v>
-      </c>
-      <c r="D1815" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="F1815" s="1" t="s">
-        <v>13</v>
+        <v>BL11</v>
       </c>
     </row>
     <row r="1816" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1816" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B1816" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="C1816" s="23" t="str">
+      <c r="A1816" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B1816" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C1816" s="56" t="str">
         <f aca="false">CONCATENATE(A1816,B1816)</f>
-        <v>BK91</v>
+        <v>BL12</v>
+      </c>
+      <c r="D1816" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1816" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1817" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1817" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B1817" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="C1817" s="23" t="str">
+      <c r="A1817" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B1817" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1817" s="56" t="str">
         <f aca="false">CONCATENATE(A1817,B1817)</f>
-        <v>BK92</v>
+        <v>BL13</v>
+      </c>
+      <c r="D1817" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1817" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1818" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1818" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B1818" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="C1818" s="23" t="str">
+      <c r="A1818" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B1818" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C1818" s="56" t="str">
         <f aca="false">CONCATENATE(A1818,B1818)</f>
-        <v>BK93</v>
+        <v>BL14</v>
+      </c>
+      <c r="D1818" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1818" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1819" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1819" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B1819" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="C1819" s="23" t="str">
+      <c r="A1819" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B1819" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C1819" s="56" t="str">
         <f aca="false">CONCATENATE(A1819,B1819)</f>
-        <v>BK94</v>
+        <v>BL15</v>
+      </c>
+      <c r="D1819" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1819" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1820" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1820" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B1820" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="C1820" s="23" t="str">
+      <c r="A1820" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B1820" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="C1820" s="56" t="str">
         <f aca="false">CONCATENATE(A1820,B1820)</f>
-        <v>BK95</v>
+        <v>BL16</v>
+      </c>
+      <c r="D1820" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1820" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1821" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1821" s="1" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B1821" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="C1821" s="23" t="str">
+      <c r="A1821" s="7" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B1821" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C1821" s="56" t="str">
         <f aca="false">CONCATENATE(A1821,B1821)</f>
-        <v>BK96</v>
+        <v>BL17</v>
+      </c>
+      <c r="D1821" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1821" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1822" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1822" s="7" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="B1822" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="C1822" s="23" t="str">
+        <v>18</v>
+      </c>
+      <c r="C1822" s="56" t="str">
         <f aca="false">CONCATENATE(A1822,B1822)</f>
-        <v>BK97</v>
+        <v>BL18</v>
+      </c>
+      <c r="D1822" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1822" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1823" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36746,17 +36830,17 @@
         <v>1233</v>
       </c>
       <c r="B1823" s="8" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C1823" s="56" t="str">
         <f aca="false">CONCATENATE(A1823,B1823)</f>
-        <v>BL1</v>
+        <v>BL19</v>
       </c>
       <c r="D1823" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1823" s="1" t="s">
-        <v>274</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1824" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36764,11 +36848,11 @@
         <v>1233</v>
       </c>
       <c r="B1824" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C1824" s="56" t="str">
+        <v>20</v>
+      </c>
+      <c r="C1824" s="82" t="str">
         <f aca="false">CONCATENATE(A1824,B1824)</f>
-        <v>BL2</v>
+        <v>BL20</v>
       </c>
       <c r="D1824" s="1" t="n">
         <v>11</v>
@@ -36782,11 +36866,11 @@
         <v>1233</v>
       </c>
       <c r="B1825" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C1825" s="56" t="str">
+        <v>21</v>
+      </c>
+      <c r="C1825" s="82" t="str">
         <f aca="false">CONCATENATE(A1825,B1825)</f>
-        <v>BL3</v>
+        <v>BL21</v>
       </c>
       <c r="D1825" s="1" t="n">
         <v>11</v>
@@ -36800,11 +36884,11 @@
         <v>1233</v>
       </c>
       <c r="B1826" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C1826" s="56" t="str">
+        <v>22</v>
+      </c>
+      <c r="C1826" s="82" t="str">
         <f aca="false">CONCATENATE(A1826,B1826)</f>
-        <v>BL4</v>
+        <v>BL22</v>
       </c>
       <c r="D1826" s="1" t="n">
         <v>11</v>
@@ -36818,17 +36902,17 @@
         <v>1233</v>
       </c>
       <c r="B1827" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C1827" s="56" t="str">
+        <v>23</v>
+      </c>
+      <c r="C1827" s="84" t="str">
         <f aca="false">CONCATENATE(A1827,B1827)</f>
-        <v>BL5</v>
+        <v>BL23</v>
       </c>
       <c r="D1827" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1827" s="1" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1828" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36836,17 +36920,17 @@
         <v>1233</v>
       </c>
       <c r="B1828" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C1828" s="56" t="str">
+        <v>24</v>
+      </c>
+      <c r="C1828" s="84" t="str">
         <f aca="false">CONCATENATE(A1828,B1828)</f>
-        <v>BL6</v>
+        <v>BL24</v>
       </c>
       <c r="D1828" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1828" s="1" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36854,17 +36938,17 @@
         <v>1233</v>
       </c>
       <c r="B1829" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C1829" s="56" t="str">
+        <v>25</v>
+      </c>
+      <c r="C1829" s="84" t="str">
         <f aca="false">CONCATENATE(A1829,B1829)</f>
-        <v>BL7</v>
+        <v>BL25</v>
       </c>
       <c r="D1829" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1829" s="1" t="s">
-        <v>274</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36872,11 +36956,17 @@
         <v>1233</v>
       </c>
       <c r="B1830" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1830" s="23" t="str">
+        <v>26</v>
+      </c>
+      <c r="C1830" s="84" t="str">
         <f aca="false">CONCATENATE(A1830,B1830)</f>
-        <v>BL8</v>
+        <v>BL26</v>
+      </c>
+      <c r="D1830" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1830" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="1831" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36884,11 +36974,17 @@
         <v>1233</v>
       </c>
       <c r="B1831" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C1831" s="23" t="str">
+        <v>27</v>
+      </c>
+      <c r="C1831" s="84" t="str">
         <f aca="false">CONCATENATE(A1831,B1831)</f>
-        <v>BL9</v>
+        <v>BL27</v>
+      </c>
+      <c r="D1831" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1831" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="1832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36896,11 +36992,17 @@
         <v>1233</v>
       </c>
       <c r="B1832" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C1832" s="23" t="str">
+        <v>28</v>
+      </c>
+      <c r="C1832" s="84" t="str">
         <f aca="false">CONCATENATE(A1832,B1832)</f>
-        <v>BL10</v>
+        <v>BL28</v>
+      </c>
+      <c r="D1832" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1832" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="1833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36908,11 +37010,17 @@
         <v>1233</v>
       </c>
       <c r="B1833" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="C1833" s="84" t="str">
+        <f aca="false">CONCATENATE(A1833,B1833)</f>
+        <v>BL29</v>
+      </c>
+      <c r="D1833" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C1833" s="23" t="str">
-        <f aca="false">CONCATENATE(A1833,B1833)</f>
-        <v>BL11</v>
+      <c r="F1833" s="1" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="1834" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36920,17 +37028,17 @@
         <v>1233</v>
       </c>
       <c r="B1834" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C1834" s="56" t="str">
+        <v>30</v>
+      </c>
+      <c r="C1834" s="84" t="str">
         <f aca="false">CONCATENATE(A1834,B1834)</f>
-        <v>BL12</v>
+        <v>BL30</v>
       </c>
       <c r="D1834" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1834" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36938,17 +37046,17 @@
         <v>1233</v>
       </c>
       <c r="B1835" s="8" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C1835" s="56" t="str">
         <f aca="false">CONCATENATE(A1835,B1835)</f>
-        <v>BL13</v>
+        <v>BL31</v>
       </c>
       <c r="D1835" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1835" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36956,17 +37064,17 @@
         <v>1233</v>
       </c>
       <c r="B1836" s="8" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C1836" s="56" t="str">
         <f aca="false">CONCATENATE(A1836,B1836)</f>
-        <v>BL14</v>
+        <v>BL32</v>
       </c>
       <c r="D1836" s="1" t="n">
         <v>11</v>
       </c>
       <c r="F1836" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1837" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36974,17 +37082,11 @@
         <v>1233</v>
       </c>
       <c r="B1837" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="C1837" s="56" t="str">
+        <v>33</v>
+      </c>
+      <c r="C1837" s="23" t="str">
         <f aca="false">CONCATENATE(A1837,B1837)</f>
-        <v>BL15</v>
-      </c>
-      <c r="D1837" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1837" s="1" t="s">
-        <v>13</v>
+        <v>BL33</v>
       </c>
     </row>
     <row r="1838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36992,17 +37094,11 @@
         <v>1233</v>
       </c>
       <c r="B1838" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="C1838" s="56" t="str">
+        <v>34</v>
+      </c>
+      <c r="C1838" s="23" t="str">
         <f aca="false">CONCATENATE(A1838,B1838)</f>
-        <v>BL16</v>
-      </c>
-      <c r="D1838" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1838" s="1" t="s">
-        <v>13</v>
+        <v>BL34</v>
       </c>
     </row>
     <row r="1839" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37010,17 +37106,11 @@
         <v>1233</v>
       </c>
       <c r="B1839" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="C1839" s="56" t="str">
+        <v>35</v>
+      </c>
+      <c r="C1839" s="23" t="str">
         <f aca="false">CONCATENATE(A1839,B1839)</f>
-        <v>BL17</v>
-      </c>
-      <c r="D1839" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1839" s="1" t="s">
-        <v>13</v>
+        <v>BL35</v>
       </c>
     </row>
     <row r="1840" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37028,17 +37118,11 @@
         <v>1233</v>
       </c>
       <c r="B1840" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C1840" s="56" t="str">
+        <v>36</v>
+      </c>
+      <c r="C1840" s="23" t="str">
         <f aca="false">CONCATENATE(A1840,B1840)</f>
-        <v>BL18</v>
-      </c>
-      <c r="D1840" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1840" s="1" t="s">
-        <v>13</v>
+        <v>BL36</v>
       </c>
     </row>
     <row r="1841" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37046,53 +37130,35 @@
         <v>1233</v>
       </c>
       <c r="B1841" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C1841" s="56" t="str">
+        <v>37</v>
+      </c>
+      <c r="C1841" s="23" t="str">
         <f aca="false">CONCATENATE(A1841,B1841)</f>
-        <v>BL19</v>
-      </c>
-      <c r="D1841" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1841" s="1" t="s">
-        <v>13</v>
+        <v>BL37</v>
       </c>
     </row>
     <row r="1842" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1842" s="1" t="s">
+      <c r="A1842" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1842" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C1842" s="81" t="str">
+      <c r="B1842" s="8" t="n">
+        <v>38</v>
+      </c>
+      <c r="C1842" s="23" t="str">
         <f aca="false">CONCATENATE(A1842,B1842)</f>
-        <v>BL20</v>
-      </c>
-      <c r="D1842" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1842" s="1" t="s">
-        <v>274</v>
+        <v>BL38</v>
       </c>
     </row>
     <row r="1843" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1843" s="1" t="s">
+      <c r="A1843" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1843" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C1843" s="81" t="str">
+      <c r="B1843" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="C1843" s="23" t="str">
         <f aca="false">CONCATENATE(A1843,B1843)</f>
-        <v>BL21</v>
-      </c>
-      <c r="D1843" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1843" s="1" t="s">
-        <v>274</v>
+        <v>BL39</v>
       </c>
     </row>
     <row r="1844" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37100,17 +37166,11 @@
         <v>1233</v>
       </c>
       <c r="B1844" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C1844" s="81" t="str">
+        <v>40</v>
+      </c>
+      <c r="C1844" s="23" t="str">
         <f aca="false">CONCATENATE(A1844,B1844)</f>
-        <v>BL22</v>
-      </c>
-      <c r="D1844" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1844" s="1" t="s">
-        <v>274</v>
+        <v>BL40</v>
       </c>
     </row>
     <row r="1845" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37118,17 +37178,11 @@
         <v>1233</v>
       </c>
       <c r="B1845" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C1845" s="84" t="str">
+        <v>41</v>
+      </c>
+      <c r="C1845" s="23" t="str">
         <f aca="false">CONCATENATE(A1845,B1845)</f>
-        <v>BL23</v>
-      </c>
-      <c r="D1845" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1845" s="1" t="s">
-        <v>8</v>
+        <v>BL41</v>
       </c>
     </row>
     <row r="1846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37136,17 +37190,11 @@
         <v>1233</v>
       </c>
       <c r="B1846" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C1846" s="84" t="str">
+        <v>42</v>
+      </c>
+      <c r="C1846" s="23" t="str">
         <f aca="false">CONCATENATE(A1846,B1846)</f>
-        <v>BL24</v>
-      </c>
-      <c r="D1846" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1846" s="1" t="s">
-        <v>8</v>
+        <v>BL42</v>
       </c>
     </row>
     <row r="1847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37154,17 +37202,11 @@
         <v>1233</v>
       </c>
       <c r="B1847" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="C1847" s="84" t="str">
+        <v>43</v>
+      </c>
+      <c r="C1847" s="23" t="str">
         <f aca="false">CONCATENATE(A1847,B1847)</f>
-        <v>BL25</v>
-      </c>
-      <c r="D1847" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1847" s="1" t="s">
-        <v>170</v>
+        <v>BL43</v>
       </c>
     </row>
     <row r="1848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37172,17 +37214,11 @@
         <v>1233</v>
       </c>
       <c r="B1848" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="C1848" s="84" t="str">
+        <v>44</v>
+      </c>
+      <c r="C1848" s="23" t="str">
         <f aca="false">CONCATENATE(A1848,B1848)</f>
-        <v>BL26</v>
-      </c>
-      <c r="D1848" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1848" s="1" t="s">
-        <v>8</v>
+        <v>BL44</v>
       </c>
     </row>
     <row r="1849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37190,17 +37226,11 @@
         <v>1233</v>
       </c>
       <c r="B1849" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="C1849" s="84" t="str">
+        <v>45</v>
+      </c>
+      <c r="C1849" s="23" t="str">
         <f aca="false">CONCATENATE(A1849,B1849)</f>
-        <v>BL27</v>
-      </c>
-      <c r="D1849" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1849" s="1" t="s">
-        <v>8</v>
+        <v>BL45</v>
       </c>
     </row>
     <row r="1850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37208,17 +37238,11 @@
         <v>1233</v>
       </c>
       <c r="B1850" s="8" t="n">
-        <v>28</v>
-      </c>
-      <c r="C1850" s="84" t="str">
+        <v>46</v>
+      </c>
+      <c r="C1850" s="23" t="str">
         <f aca="false">CONCATENATE(A1850,B1850)</f>
-        <v>BL28</v>
-      </c>
-      <c r="D1850" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1850" s="1" t="s">
-        <v>8</v>
+        <v>BL46</v>
       </c>
     </row>
     <row r="1851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37226,17 +37250,11 @@
         <v>1233</v>
       </c>
       <c r="B1851" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="C1851" s="84" t="str">
+        <v>47</v>
+      </c>
+      <c r="C1851" s="23" t="str">
         <f aca="false">CONCATENATE(A1851,B1851)</f>
-        <v>BL29</v>
-      </c>
-      <c r="D1851" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1851" s="1" t="s">
-        <v>170</v>
+        <v>BL47</v>
       </c>
     </row>
     <row r="1852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37244,17 +37262,11 @@
         <v>1233</v>
       </c>
       <c r="B1852" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="C1852" s="84" t="str">
+        <v>48</v>
+      </c>
+      <c r="C1852" s="23" t="str">
         <f aca="false">CONCATENATE(A1852,B1852)</f>
-        <v>BL30</v>
-      </c>
-      <c r="D1852" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1852" s="1" t="s">
-        <v>8</v>
+        <v>BL48</v>
       </c>
     </row>
     <row r="1853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37262,17 +37274,11 @@
         <v>1233</v>
       </c>
       <c r="B1853" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="C1853" s="56" t="str">
+        <v>49</v>
+      </c>
+      <c r="C1853" s="23" t="str">
         <f aca="false">CONCATENATE(A1853,B1853)</f>
-        <v>BL31</v>
-      </c>
-      <c r="D1853" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1853" s="1" t="s">
-        <v>8</v>
+        <v>BL49</v>
       </c>
     </row>
     <row r="1854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37280,17 +37286,11 @@
         <v>1233</v>
       </c>
       <c r="B1854" s="8" t="n">
-        <v>32</v>
-      </c>
-      <c r="C1854" s="56" t="str">
+        <v>50</v>
+      </c>
+      <c r="C1854" s="23" t="str">
         <f aca="false">CONCATENATE(A1854,B1854)</f>
-        <v>BL32</v>
-      </c>
-      <c r="D1854" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1854" s="1" t="s">
-        <v>33</v>
+        <v>BL50</v>
       </c>
     </row>
     <row r="1855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37298,11 +37298,11 @@
         <v>1233</v>
       </c>
       <c r="B1855" s="8" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C1855" s="23" t="str">
         <f aca="false">CONCATENATE(A1855,B1855)</f>
-        <v>BL33</v>
+        <v>BL51</v>
       </c>
     </row>
     <row r="1856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37310,11 +37310,17 @@
         <v>1233</v>
       </c>
       <c r="B1856" s="8" t="n">
-        <v>34</v>
-      </c>
-      <c r="C1856" s="23" t="str">
+        <v>52</v>
+      </c>
+      <c r="C1856" s="82" t="str">
         <f aca="false">CONCATENATE(A1856,B1856)</f>
-        <v>BL34</v>
+        <v>BL52</v>
+      </c>
+      <c r="D1856" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1856" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37322,11 +37328,17 @@
         <v>1233</v>
       </c>
       <c r="B1857" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="C1857" s="23" t="str">
+        <v>53</v>
+      </c>
+      <c r="C1857" s="82" t="str">
         <f aca="false">CONCATENATE(A1857,B1857)</f>
-        <v>BL35</v>
+        <v>BL53</v>
+      </c>
+      <c r="D1857" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1857" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1858" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37334,11 +37346,17 @@
         <v>1233</v>
       </c>
       <c r="B1858" s="8" t="n">
-        <v>36</v>
-      </c>
-      <c r="C1858" s="23" t="str">
+        <v>54</v>
+      </c>
+      <c r="C1858" s="82" t="str">
         <f aca="false">CONCATENATE(A1858,B1858)</f>
-        <v>BL36</v>
+        <v>BL54</v>
+      </c>
+      <c r="D1858" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1858" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1859" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37346,11 +37364,17 @@
         <v>1233</v>
       </c>
       <c r="B1859" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="C1859" s="23" t="str">
+        <v>55</v>
+      </c>
+      <c r="C1859" s="82" t="str">
         <f aca="false">CONCATENATE(A1859,B1859)</f>
-        <v>BL37</v>
+        <v>BL55</v>
+      </c>
+      <c r="D1859" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1859" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1860" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37358,11 +37382,17 @@
         <v>1233</v>
       </c>
       <c r="B1860" s="8" t="n">
-        <v>38</v>
-      </c>
-      <c r="C1860" s="23" t="str">
+        <v>56</v>
+      </c>
+      <c r="C1860" s="82" t="str">
         <f aca="false">CONCATENATE(A1860,B1860)</f>
-        <v>BL38</v>
+        <v>BL56</v>
+      </c>
+      <c r="D1860" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1860" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1861" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37370,11 +37400,17 @@
         <v>1233</v>
       </c>
       <c r="B1861" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="C1861" s="23" t="str">
+        <v>57</v>
+      </c>
+      <c r="C1861" s="82" t="str">
         <f aca="false">CONCATENATE(A1861,B1861)</f>
-        <v>BL39</v>
+        <v>BL57</v>
+      </c>
+      <c r="D1861" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1861" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1862" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37382,11 +37418,17 @@
         <v>1233</v>
       </c>
       <c r="B1862" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="C1862" s="23" t="str">
+        <v>58</v>
+      </c>
+      <c r="C1862" s="82" t="str">
         <f aca="false">CONCATENATE(A1862,B1862)</f>
-        <v>BL40</v>
+        <v>BL58</v>
+      </c>
+      <c r="D1862" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1862" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1863" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37394,11 +37436,17 @@
         <v>1233</v>
       </c>
       <c r="B1863" s="8" t="n">
-        <v>41</v>
-      </c>
-      <c r="C1863" s="23" t="str">
+        <v>59</v>
+      </c>
+      <c r="C1863" s="82" t="str">
         <f aca="false">CONCATENATE(A1863,B1863)</f>
-        <v>BL41</v>
+        <v>BL59</v>
+      </c>
+      <c r="D1863" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1863" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1864" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37406,11 +37454,17 @@
         <v>1233</v>
       </c>
       <c r="B1864" s="8" t="n">
-        <v>42</v>
-      </c>
-      <c r="C1864" s="23" t="str">
+        <v>60</v>
+      </c>
+      <c r="C1864" s="82" t="str">
         <f aca="false">CONCATENATE(A1864,B1864)</f>
-        <v>BL42</v>
+        <v>BL60</v>
+      </c>
+      <c r="D1864" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1864" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1865" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37418,11 +37472,11 @@
         <v>1233</v>
       </c>
       <c r="B1865" s="8" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C1865" s="23" t="str">
         <f aca="false">CONCATENATE(A1865,B1865)</f>
-        <v>BL43</v>
+        <v>BL61</v>
       </c>
     </row>
     <row r="1866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37430,11 +37484,17 @@
         <v>1233</v>
       </c>
       <c r="B1866" s="8" t="n">
-        <v>44</v>
-      </c>
-      <c r="C1866" s="23" t="str">
+        <v>62</v>
+      </c>
+      <c r="C1866" s="82" t="str">
         <f aca="false">CONCATENATE(A1866,B1866)</f>
-        <v>BL44</v>
+        <v>BL62</v>
+      </c>
+      <c r="D1866" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1866" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37442,11 +37502,17 @@
         <v>1233</v>
       </c>
       <c r="B1867" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="C1867" s="23" t="str">
+        <v>63</v>
+      </c>
+      <c r="C1867" s="82" t="str">
         <f aca="false">CONCATENATE(A1867,B1867)</f>
-        <v>BL45</v>
+        <v>BL63</v>
+      </c>
+      <c r="D1867" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1867" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37454,11 +37520,17 @@
         <v>1233</v>
       </c>
       <c r="B1868" s="8" t="n">
-        <v>46</v>
-      </c>
-      <c r="C1868" s="23" t="str">
+        <v>64</v>
+      </c>
+      <c r="C1868" s="82" t="str">
         <f aca="false">CONCATENATE(A1868,B1868)</f>
-        <v>BL46</v>
+        <v>BL64</v>
+      </c>
+      <c r="D1868" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1868" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37466,11 +37538,17 @@
         <v>1233</v>
       </c>
       <c r="B1869" s="8" t="n">
-        <v>47</v>
-      </c>
-      <c r="C1869" s="23" t="str">
+        <v>65</v>
+      </c>
+      <c r="C1869" s="82" t="str">
         <f aca="false">CONCATENATE(A1869,B1869)</f>
-        <v>BL47</v>
+        <v>BL65</v>
+      </c>
+      <c r="D1869" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1869" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37478,11 +37556,17 @@
         <v>1233</v>
       </c>
       <c r="B1870" s="8" t="n">
-        <v>48</v>
-      </c>
-      <c r="C1870" s="23" t="str">
+        <v>66</v>
+      </c>
+      <c r="C1870" s="82" t="str">
         <f aca="false">CONCATENATE(A1870,B1870)</f>
-        <v>BL48</v>
+        <v>BL66</v>
+      </c>
+      <c r="D1870" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1870" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37490,11 +37574,17 @@
         <v>1233</v>
       </c>
       <c r="B1871" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="C1871" s="23" t="str">
+        <v>67</v>
+      </c>
+      <c r="C1871" s="82" t="str">
         <f aca="false">CONCATENATE(A1871,B1871)</f>
-        <v>BL49</v>
+        <v>BL67</v>
+      </c>
+      <c r="D1871" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1871" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1872" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37502,11 +37592,17 @@
         <v>1233</v>
       </c>
       <c r="B1872" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="C1872" s="23" t="str">
+        <v>68</v>
+      </c>
+      <c r="C1872" s="82" t="str">
         <f aca="false">CONCATENATE(A1872,B1872)</f>
-        <v>BL50</v>
+        <v>BL68</v>
+      </c>
+      <c r="D1872" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1872" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1873" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37514,11 +37610,17 @@
         <v>1233</v>
       </c>
       <c r="B1873" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="C1873" s="23" t="str">
+        <v>69</v>
+      </c>
+      <c r="C1873" s="82" t="str">
         <f aca="false">CONCATENATE(A1873,B1873)</f>
-        <v>BL51</v>
+        <v>BL69</v>
+      </c>
+      <c r="D1873" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1873" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1874" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37526,11 +37628,11 @@
         <v>1233</v>
       </c>
       <c r="B1874" s="8" t="n">
-        <v>52</v>
-      </c>
-      <c r="C1874" s="81" t="str">
+        <v>70</v>
+      </c>
+      <c r="C1874" s="82" t="str">
         <f aca="false">CONCATENATE(A1874,B1874)</f>
-        <v>BL52</v>
+        <v>BL70</v>
       </c>
       <c r="D1874" s="1" t="n">
         <v>11</v>
@@ -37544,11 +37646,11 @@
         <v>1233</v>
       </c>
       <c r="B1875" s="8" t="n">
-        <v>53</v>
-      </c>
-      <c r="C1875" s="81" t="str">
+        <v>71</v>
+      </c>
+      <c r="C1875" s="82" t="str">
         <f aca="false">CONCATENATE(A1875,B1875)</f>
-        <v>BL53</v>
+        <v>BL71</v>
       </c>
       <c r="D1875" s="1" t="n">
         <v>11</v>
@@ -37562,11 +37664,11 @@
         <v>1233</v>
       </c>
       <c r="B1876" s="8" t="n">
-        <v>54</v>
-      </c>
-      <c r="C1876" s="81" t="str">
+        <v>72</v>
+      </c>
+      <c r="C1876" s="82" t="str">
         <f aca="false">CONCATENATE(A1876,B1876)</f>
-        <v>BL54</v>
+        <v>BL72</v>
       </c>
       <c r="D1876" s="1" t="n">
         <v>11</v>
@@ -37580,11 +37682,11 @@
         <v>1233</v>
       </c>
       <c r="B1877" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="C1877" s="81" t="str">
+        <v>73</v>
+      </c>
+      <c r="C1877" s="82" t="str">
         <f aca="false">CONCATENATE(A1877,B1877)</f>
-        <v>BL55</v>
+        <v>BL73</v>
       </c>
       <c r="D1877" s="1" t="n">
         <v>11</v>
@@ -37598,11 +37700,11 @@
         <v>1233</v>
       </c>
       <c r="B1878" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="C1878" s="81" t="str">
+        <v>74</v>
+      </c>
+      <c r="C1878" s="82" t="str">
         <f aca="false">CONCATENATE(A1878,B1878)</f>
-        <v>BL56</v>
+        <v>BL74</v>
       </c>
       <c r="D1878" s="1" t="n">
         <v>11</v>
@@ -37616,11 +37718,11 @@
         <v>1233</v>
       </c>
       <c r="B1879" s="8" t="n">
-        <v>57</v>
-      </c>
-      <c r="C1879" s="81" t="str">
+        <v>75</v>
+      </c>
+      <c r="C1879" s="82" t="str">
         <f aca="false">CONCATENATE(A1879,B1879)</f>
-        <v>BL57</v>
+        <v>BL75</v>
       </c>
       <c r="D1879" s="1" t="n">
         <v>11</v>
@@ -37634,11 +37736,11 @@
         <v>1233</v>
       </c>
       <c r="B1880" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="C1880" s="81" t="str">
+        <v>76</v>
+      </c>
+      <c r="C1880" s="82" t="str">
         <f aca="false">CONCATENATE(A1880,B1880)</f>
-        <v>BL58</v>
+        <v>BL76</v>
       </c>
       <c r="D1880" s="1" t="n">
         <v>11</v>
@@ -37652,11 +37754,11 @@
         <v>1233</v>
       </c>
       <c r="B1881" s="8" t="n">
-        <v>59</v>
-      </c>
-      <c r="C1881" s="81" t="str">
+        <v>77</v>
+      </c>
+      <c r="C1881" s="82" t="str">
         <f aca="false">CONCATENATE(A1881,B1881)</f>
-        <v>BL59</v>
+        <v>BL77</v>
       </c>
       <c r="D1881" s="1" t="n">
         <v>11</v>
@@ -37670,11 +37772,11 @@
         <v>1233</v>
       </c>
       <c r="B1882" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="C1882" s="81" t="str">
+        <v>78</v>
+      </c>
+      <c r="C1882" s="82" t="str">
         <f aca="false">CONCATENATE(A1882,B1882)</f>
-        <v>BL60</v>
+        <v>BL78</v>
       </c>
       <c r="D1882" s="1" t="n">
         <v>11</v>
@@ -37688,11 +37790,17 @@
         <v>1233</v>
       </c>
       <c r="B1883" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="C1883" s="23" t="str">
+        <v>79</v>
+      </c>
+      <c r="C1883" s="82" t="str">
         <f aca="false">CONCATENATE(A1883,B1883)</f>
-        <v>BL61</v>
+        <v>BL79</v>
+      </c>
+      <c r="D1883" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1883" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37700,11 +37808,11 @@
         <v>1233</v>
       </c>
       <c r="B1884" s="8" t="n">
-        <v>62</v>
-      </c>
-      <c r="C1884" s="81" t="str">
+        <v>80</v>
+      </c>
+      <c r="C1884" s="82" t="str">
         <f aca="false">CONCATENATE(A1884,B1884)</f>
-        <v>BL62</v>
+        <v>BL80</v>
       </c>
       <c r="D1884" s="1" t="n">
         <v>11</v>
@@ -37714,291 +37822,257 @@
       </c>
     </row>
     <row r="1885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1885" s="1" t="s">
+      <c r="A1885" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1885" s="2" t="n">
-        <v>63</v>
-      </c>
-      <c r="C1885" s="81" t="str">
-        <f aca="false">CONCATENATE(A1885,B1885)</f>
-        <v>BL63</v>
-      </c>
-      <c r="D1885" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1885" s="1" t="s">
-        <v>274</v>
+      <c r="B1885" s="8" t="n">
+        <v>81</v>
+      </c>
+      <c r="C1885" s="10" t="s">
+        <v>1234</v>
       </c>
     </row>
     <row r="1886" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1886" s="1" t="s">
+      <c r="A1886" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1886" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="C1886" s="81" t="str">
-        <f aca="false">CONCATENATE(A1886,B1886)</f>
-        <v>BL64</v>
+      <c r="B1886" s="8" t="n">
+        <v>82</v>
+      </c>
+      <c r="C1886" s="85" t="s">
+        <v>1235</v>
       </c>
       <c r="D1886" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1886" s="1" t="s">
-        <v>274</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1887" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1887" s="1" t="s">
+      <c r="A1887" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1887" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="C1887" s="81" t="str">
-        <f aca="false">CONCATENATE(A1887,B1887)</f>
-        <v>BL65</v>
+      <c r="B1887" s="8" t="n">
+        <v>83</v>
+      </c>
+      <c r="C1887" s="85" t="s">
+        <v>1236</v>
       </c>
       <c r="D1887" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1887" s="1" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1888" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1888" s="1" t="s">
+      <c r="A1888" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1888" s="2" t="n">
-        <v>66</v>
-      </c>
-      <c r="C1888" s="81" t="str">
-        <f aca="false">CONCATENATE(A1888,B1888)</f>
-        <v>BL66</v>
+      <c r="B1888" s="8" t="n">
+        <v>84</v>
+      </c>
+      <c r="C1888" s="85" t="s">
+        <v>1237</v>
       </c>
       <c r="D1888" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1888" s="1" t="s">
-        <v>274</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1889" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1889" s="1" t="s">
+      <c r="A1889" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1889" s="2" t="n">
-        <v>67</v>
-      </c>
-      <c r="C1889" s="81" t="str">
-        <f aca="false">CONCATENATE(A1889,B1889)</f>
-        <v>BL67</v>
+      <c r="B1889" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="C1889" s="85" t="s">
+        <v>1238</v>
       </c>
       <c r="D1889" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1889" s="1" t="s">
-        <v>274</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1890" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1890" s="1" t="s">
+      <c r="A1890" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1890" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="C1890" s="81" t="str">
-        <f aca="false">CONCATENATE(A1890,B1890)</f>
-        <v>BL68</v>
+      <c r="B1890" s="8" t="n">
+        <v>86</v>
+      </c>
+      <c r="C1890" s="85" t="s">
+        <v>1239</v>
       </c>
       <c r="D1890" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1890" s="1" t="s">
-        <v>274</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="1891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1891" s="1" t="s">
+      <c r="A1891" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1891" s="2" t="n">
-        <v>69</v>
-      </c>
-      <c r="C1891" s="81" t="str">
-        <f aca="false">CONCATENATE(A1891,B1891)</f>
-        <v>BL69</v>
-      </c>
-      <c r="D1891" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1891" s="1" t="s">
-        <v>274</v>
+      <c r="B1891" s="8" t="n">
+        <v>87</v>
+      </c>
+      <c r="C1891" s="10" t="s">
+        <v>1240</v>
       </c>
     </row>
     <row r="1892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1892" s="1" t="s">
+      <c r="A1892" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1892" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="C1892" s="81" t="str">
-        <f aca="false">CONCATENATE(A1892,B1892)</f>
-        <v>BL70</v>
+      <c r="B1892" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="C1892" s="85" t="s">
+        <v>1241</v>
       </c>
       <c r="D1892" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1892" s="1" t="s">
-        <v>274</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1893" s="1" t="s">
+      <c r="A1893" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1893" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="C1893" s="81" t="str">
-        <f aca="false">CONCATENATE(A1893,B1893)</f>
-        <v>BL71</v>
+      <c r="B1893" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="C1893" s="42" t="s">
+        <v>1242</v>
       </c>
       <c r="D1893" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
+      </c>
+      <c r="E1893" s="3" t="s">
+        <v>1243</v>
       </c>
       <c r="F1893" s="1" t="s">
-        <v>274</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="1894" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1894" s="1" t="s">
+      <c r="A1894" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1894" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="C1894" s="81" t="str">
-        <f aca="false">CONCATENATE(A1894,B1894)</f>
-        <v>BL72</v>
+      <c r="B1894" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="C1894" s="42" t="s">
+        <v>1245</v>
       </c>
       <c r="D1894" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1894" s="1" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1895" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1895" s="1" t="s">
+      <c r="A1895" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1895" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="C1895" s="81" t="str">
-        <f aca="false">CONCATENATE(A1895,B1895)</f>
-        <v>BL73</v>
+      <c r="B1895" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="C1895" s="42" t="s">
+        <v>1246</v>
       </c>
       <c r="D1895" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1895" s="1" t="s">
-        <v>274</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1896" s="1" t="s">
+      <c r="A1896" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1896" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="C1896" s="81" t="str">
-        <f aca="false">CONCATENATE(A1896,B1896)</f>
-        <v>BL74</v>
+      <c r="B1896" s="8" t="n">
+        <v>92</v>
+      </c>
+      <c r="C1896" s="42" t="s">
+        <v>1247</v>
       </c>
       <c r="D1896" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1896" s="1" t="s">
-        <v>274</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1897" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1897" s="1" t="s">
+      <c r="A1897" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1897" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="C1897" s="81" t="str">
-        <f aca="false">CONCATENATE(A1897,B1897)</f>
-        <v>BL75</v>
+      <c r="B1897" s="8" t="n">
+        <v>93</v>
+      </c>
+      <c r="C1897" s="42" t="s">
+        <v>1248</v>
       </c>
       <c r="D1897" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1897" s="1" t="s">
-        <v>274</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1898" s="1" t="s">
+      <c r="A1898" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1898" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="C1898" s="81" t="str">
-        <f aca="false">CONCATENATE(A1898,B1898)</f>
-        <v>BL76</v>
+      <c r="B1898" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="C1898" s="42" t="s">
+        <v>1249</v>
       </c>
       <c r="D1898" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1898" s="1" t="s">
-        <v>274</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1899" s="1" t="s">
+      <c r="A1899" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1899" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="C1899" s="81" t="str">
-        <f aca="false">CONCATENATE(A1899,B1899)</f>
-        <v>BL77</v>
-      </c>
-      <c r="D1899" s="1" t="n">
-        <v>11</v>
+      <c r="B1899" s="8" t="n">
+        <v>95</v>
+      </c>
+      <c r="C1899" s="10" t="s">
+        <v>1250</v>
       </c>
       <c r="F1899" s="1" t="s">
-        <v>274</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1900" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1900" s="1" t="s">
+      <c r="A1900" s="7" t="s">
         <v>1233</v>
       </c>
-      <c r="B1900" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="C1900" s="81" t="str">
-        <f aca="false">CONCATENATE(A1900,B1900)</f>
-        <v>BL78</v>
-      </c>
-      <c r="D1900" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="F1900" s="1" t="s">
-        <v>274</v>
+      <c r="B1900" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="C1900" s="10" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="1901" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38006,14 +38080,13 @@
         <v>1233</v>
       </c>
       <c r="B1901" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="C1901" s="81" t="str">
-        <f aca="false">CONCATENATE(A1901,B1901)</f>
-        <v>BL79</v>
+        <v>97</v>
+      </c>
+      <c r="C1901" s="85" t="s">
+        <v>1252</v>
       </c>
       <c r="D1901" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1901" s="1" t="s">
         <v>274</v>
@@ -38024,17 +38097,16 @@
         <v>1233</v>
       </c>
       <c r="B1902" s="8" t="n">
-        <v>80</v>
-      </c>
-      <c r="C1902" s="81" t="str">
-        <f aca="false">CONCATENATE(A1902,B1902)</f>
-        <v>BL80</v>
+        <v>98</v>
+      </c>
+      <c r="C1902" s="42" t="s">
+        <v>1253</v>
       </c>
       <c r="D1902" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F1902" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1903" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38042,10 +38114,16 @@
         <v>1233</v>
       </c>
       <c r="B1903" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="C1903" s="10" t="s">
-        <v>1234</v>
+        <v>99</v>
+      </c>
+      <c r="C1903" s="86" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D1903" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1903" s="1" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="1904" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38053,16 +38131,16 @@
         <v>1233</v>
       </c>
       <c r="B1904" s="8" t="n">
-        <v>82</v>
-      </c>
-      <c r="C1904" s="85" t="s">
-        <v>1235</v>
+        <v>100</v>
+      </c>
+      <c r="C1904" s="86" t="s">
+        <v>1255</v>
       </c>
       <c r="D1904" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F1904" s="1" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1905" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38070,16 +38148,16 @@
         <v>1233</v>
       </c>
       <c r="B1905" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="C1905" s="85" t="s">
-        <v>1236</v>
+        <v>101</v>
+      </c>
+      <c r="C1905" s="86" t="s">
+        <v>1256</v>
       </c>
       <c r="D1905" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F1905" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1906" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38087,16 +38165,16 @@
         <v>1233</v>
       </c>
       <c r="B1906" s="8" t="n">
-        <v>84</v>
-      </c>
-      <c r="C1906" s="85" t="s">
-        <v>1237</v>
+        <v>102</v>
+      </c>
+      <c r="C1906" s="86" t="s">
+        <v>1257</v>
       </c>
       <c r="D1906" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F1906" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1907" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38104,16 +38182,13 @@
         <v>1233</v>
       </c>
       <c r="B1907" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="C1907" s="85" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D1907" s="1" t="n">
-        <v>4</v>
+        <v>103</v>
+      </c>
+      <c r="C1907" s="87" t="s">
+        <v>1258</v>
       </c>
       <c r="F1907" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38121,16 +38196,13 @@
         <v>1233</v>
       </c>
       <c r="B1908" s="8" t="n">
-        <v>86</v>
-      </c>
-      <c r="C1908" s="85" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D1908" s="1" t="n">
-        <v>4</v>
+        <v>104</v>
+      </c>
+      <c r="C1908" s="87" t="s">
+        <v>1259</v>
       </c>
       <c r="F1908" s="1" t="s">
-        <v>1091</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38138,10 +38210,16 @@
         <v>1233</v>
       </c>
       <c r="B1909" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="C1909" s="10" t="s">
-        <v>1240</v>
+        <v>105</v>
+      </c>
+      <c r="C1909" s="86" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D1909" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1909" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="1910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38149,16 +38227,16 @@
         <v>1233</v>
       </c>
       <c r="B1910" s="8" t="n">
-        <v>88</v>
-      </c>
-      <c r="C1910" s="85" t="s">
-        <v>1241</v>
+        <v>106</v>
+      </c>
+      <c r="C1910" s="86" t="s">
+        <v>1261</v>
       </c>
       <c r="D1910" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F1910" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38166,19 +38244,16 @@
         <v>1233</v>
       </c>
       <c r="B1911" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="C1911" s="42" t="s">
-        <v>1242</v>
+        <v>107</v>
+      </c>
+      <c r="C1911" s="86" t="s">
+        <v>1262</v>
       </c>
       <c r="D1911" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E1911" s="3" t="s">
-        <v>1243</v>
-      </c>
       <c r="F1911" s="1" t="s">
-        <v>1244</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38186,16 +38261,16 @@
         <v>1233</v>
       </c>
       <c r="B1912" s="8" t="n">
-        <v>90</v>
-      </c>
-      <c r="C1912" s="42" t="s">
-        <v>1245</v>
+        <v>108</v>
+      </c>
+      <c r="C1912" s="86" t="s">
+        <v>1263</v>
       </c>
       <c r="D1912" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F1912" s="1" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38203,106 +38278,121 @@
         <v>1233</v>
       </c>
       <c r="B1913" s="8" t="n">
-        <v>91</v>
-      </c>
-      <c r="C1913" s="42" t="s">
-        <v>1246</v>
+        <v>109</v>
+      </c>
+      <c r="C1913" s="86" t="s">
+        <v>1264</v>
       </c>
       <c r="D1913" s="1" t="n">
         <v>4</v>
       </c>
       <c r="F1913" s="1" t="s">
-        <v>33</v>
+        <v>276</v>
       </c>
     </row>
     <row r="1914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1914" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1914" s="8" t="n">
-        <v>92</v>
-      </c>
-      <c r="C1914" s="42" t="s">
-        <v>1247</v>
+        <v>1</v>
+      </c>
+      <c r="C1914" s="88" t="str">
+        <f aca="false">CONCATENATE(A1914,B1914)</f>
+        <v>BM1</v>
       </c>
       <c r="D1914" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1914" s="1" t="s">
-        <v>13</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1915" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1915" s="8" t="n">
-        <v>93</v>
-      </c>
-      <c r="C1915" s="42" t="s">
-        <v>1248</v>
+        <v>2</v>
+      </c>
+      <c r="C1915" s="88" t="str">
+        <f aca="false">CONCATENATE(A1915,B1915)</f>
+        <v>BM2</v>
       </c>
       <c r="D1915" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1915" s="1" t="s">
-        <v>13</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1916" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1916" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="C1916" s="42" t="s">
-        <v>1249</v>
+        <v>3</v>
+      </c>
+      <c r="C1916" s="88" t="str">
+        <f aca="false">CONCATENATE(A1916,B1916)</f>
+        <v>BM3</v>
       </c>
       <c r="D1916" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1916" s="1" t="s">
-        <v>13</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1917" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1917" s="8" t="n">
-        <v>95</v>
-      </c>
-      <c r="C1917" s="10" t="s">
-        <v>1250</v>
+        <v>4</v>
+      </c>
+      <c r="C1917" s="88" t="str">
+        <f aca="false">CONCATENATE(A1917,B1917)</f>
+        <v>BM4</v>
+      </c>
+      <c r="D1917" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="F1917" s="1" t="s">
-        <v>99</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1918" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1918" s="8" t="n">
-        <v>96</v>
-      </c>
-      <c r="C1918" s="10" t="s">
-        <v>1251</v>
+        <v>5</v>
+      </c>
+      <c r="C1918" s="88" t="str">
+        <f aca="false">CONCATENATE(A1918,B1918)</f>
+        <v>BM5</v>
+      </c>
+      <c r="D1918" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1918" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="1919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1919" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1919" s="8" t="n">
-        <v>97</v>
-      </c>
-      <c r="C1919" s="85" t="s">
-        <v>1252</v>
+        <v>6</v>
+      </c>
+      <c r="C1919" s="88" t="str">
+        <f aca="false">CONCATENATE(A1919,B1919)</f>
+        <v>BM6</v>
       </c>
       <c r="D1919" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1919" s="1" t="s">
         <v>274</v>
@@ -38310,200 +38400,194 @@
     </row>
     <row r="1920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1920" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1920" s="8" t="n">
-        <v>98</v>
-      </c>
-      <c r="C1920" s="42" t="s">
-        <v>1253</v>
+        <v>7</v>
+      </c>
+      <c r="C1920" s="88" t="str">
+        <f aca="false">CONCATENATE(A1920,B1920)</f>
+        <v>BM7</v>
       </c>
       <c r="D1920" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1920" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1921" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1921" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1921" s="8" t="n">
-        <v>99</v>
-      </c>
-      <c r="C1921" s="86" t="s">
-        <v>1254</v>
+        <v>8</v>
+      </c>
+      <c r="C1921" s="88" t="str">
+        <f aca="false">CONCATENATE(A1921,B1921)</f>
+        <v>BM8</v>
       </c>
       <c r="D1921" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1921" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1922" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1922" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="C1922" s="86" t="s">
-        <v>1255</v>
+        <v>9</v>
+      </c>
+      <c r="C1922" s="88" t="str">
+        <f aca="false">CONCATENATE(A1922,B1922)</f>
+        <v>BM9</v>
       </c>
       <c r="D1922" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1922" s="1" t="s">
-        <v>8</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1923" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1923" s="8" t="n">
-        <v>101</v>
-      </c>
-      <c r="C1923" s="86" t="s">
-        <v>1256</v>
+        <v>10</v>
+      </c>
+      <c r="C1923" s="88" t="str">
+        <f aca="false">CONCATENATE(A1923,B1923)</f>
+        <v>BM10</v>
       </c>
       <c r="D1923" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1923" s="1" t="s">
-        <v>13</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1924" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1924" s="8" t="n">
-        <v>102</v>
-      </c>
-      <c r="C1924" s="86" t="s">
-        <v>1257</v>
+        <v>11</v>
+      </c>
+      <c r="C1924" s="29" t="str">
+        <f aca="false">CONCATENATE(A1924,B1924)</f>
+        <v>BM11</v>
       </c>
       <c r="D1924" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1924" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1925" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1925" s="8" t="n">
-        <v>103</v>
-      </c>
-      <c r="C1925" s="87" t="s">
-        <v>1258</v>
+        <v>12</v>
+      </c>
+      <c r="C1925" s="29" t="str">
+        <f aca="false">CONCATENATE(A1925,B1925)</f>
+        <v>BM12</v>
+      </c>
+      <c r="D1925" s="1" t="n">
+        <v>9</v>
       </c>
       <c r="F1925" s="1" t="s">
-        <v>8</v>
+        <v>274</v>
       </c>
     </row>
     <row r="1926" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1926" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1926" s="8" t="n">
-        <v>104</v>
-      </c>
-      <c r="C1926" s="87" t="s">
-        <v>1259</v>
-      </c>
-      <c r="F1926" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="C1926" s="23" t="str">
+        <f aca="false">CONCATENATE(A1926,B1926)</f>
+        <v>BM13</v>
       </c>
     </row>
     <row r="1927" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1927" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1927" s="8" t="n">
-        <v>105</v>
-      </c>
-      <c r="C1927" s="86" t="s">
-        <v>1260</v>
-      </c>
-      <c r="D1927" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="F1927" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
+      </c>
+      <c r="C1927" s="23" t="str">
+        <f aca="false">CONCATENATE(A1927,B1927)</f>
+        <v>BM14</v>
       </c>
     </row>
     <row r="1928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1928" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1928" s="8" t="n">
-        <v>106</v>
-      </c>
-      <c r="C1928" s="86" t="s">
-        <v>1261</v>
-      </c>
-      <c r="D1928" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="F1928" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
+      </c>
+      <c r="C1928" s="23" t="str">
+        <f aca="false">CONCATENATE(A1928,B1928)</f>
+        <v>BM15</v>
       </c>
     </row>
     <row r="1929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1929" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1929" s="8" t="n">
-        <v>107</v>
-      </c>
-      <c r="C1929" s="86" t="s">
-        <v>1262</v>
-      </c>
-      <c r="D1929" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="F1929" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
+      </c>
+      <c r="C1929" s="23" t="str">
+        <f aca="false">CONCATENATE(A1929,B1929)</f>
+        <v>BM16</v>
       </c>
     </row>
     <row r="1930" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1930" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1930" s="8" t="n">
-        <v>108</v>
-      </c>
-      <c r="C1930" s="86" t="s">
-        <v>1263</v>
+        <v>17</v>
+      </c>
+      <c r="C1930" s="89" t="str">
+        <f aca="false">CONCATENATE(A1930,B1930)</f>
+        <v>BM17</v>
       </c>
       <c r="D1930" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1930" s="1" t="s">
-        <v>99</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1931" s="7" t="s">
-        <v>1233</v>
+        <v>1265</v>
       </c>
       <c r="B1931" s="8" t="n">
-        <v>109</v>
-      </c>
-      <c r="C1931" s="86" t="s">
-        <v>1264</v>
+        <v>18</v>
+      </c>
+      <c r="C1931" s="89" t="str">
+        <f aca="false">CONCATENATE(A1931,B1931)</f>
+        <v>BM18</v>
       </c>
       <c r="D1931" s="1" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F1931" s="1" t="s">
-        <v>276</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1932" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38511,17 +38595,17 @@
         <v>1265</v>
       </c>
       <c r="B1932" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1932" s="88" t="str">
+        <v>19</v>
+      </c>
+      <c r="C1932" s="89" t="str">
         <f aca="false">CONCATENATE(A1932,B1932)</f>
-        <v>BM1</v>
+        <v>BM19</v>
       </c>
       <c r="D1932" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F1932" s="1" t="s">
-        <v>274</v>
+        <v>170</v>
       </c>
     </row>
     <row r="1933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38529,17 +38613,17 @@
         <v>1265</v>
       </c>
       <c r="B1933" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C1933" s="88" t="str">
+        <v>20</v>
+      </c>
+      <c r="C1933" s="89" t="str">
         <f aca="false">CONCATENATE(A1933,B1933)</f>
-        <v>BM2</v>
+        <v>BM20</v>
       </c>
       <c r="D1933" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F1933" s="1" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38547,11 +38631,11 @@
         <v>1265</v>
       </c>
       <c r="B1934" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C1934" s="88" t="str">
+        <v>21</v>
+      </c>
+      <c r="C1934" s="89" t="str">
         <f aca="false">CONCATENATE(A1934,B1934)</f>
-        <v>BM3</v>
+        <v>BM21</v>
       </c>
       <c r="D1934" s="1" t="n">
         <v>9</v>
@@ -38565,17 +38649,17 @@
         <v>1265</v>
       </c>
       <c r="B1935" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C1935" s="88" t="str">
+        <v>22</v>
+      </c>
+      <c r="C1935" s="89" t="str">
         <f aca="false">CONCATENATE(A1935,B1935)</f>
-        <v>BM4</v>
+        <v>BM22</v>
       </c>
       <c r="D1935" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F1935" s="1" t="s">
-        <v>274</v>
+        <v>183</v>
       </c>
     </row>
     <row r="1936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38583,17 +38667,17 @@
         <v>1265</v>
       </c>
       <c r="B1936" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="C1936" s="88" t="str">
+        <v>23</v>
+      </c>
+      <c r="C1936" s="89" t="str">
         <f aca="false">CONCATENATE(A1936,B1936)</f>
-        <v>BM5</v>
+        <v>BM23</v>
       </c>
       <c r="D1936" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F1936" s="1" t="s">
-        <v>274</v>
+        <v>99</v>
       </c>
     </row>
     <row r="1937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38601,17 +38685,17 @@
         <v>1265</v>
       </c>
       <c r="B1937" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C1937" s="88" t="str">
+        <v>24</v>
+      </c>
+      <c r="C1937" s="89" t="str">
         <f aca="false">CONCATENATE(A1937,B1937)</f>
-        <v>BM6</v>
+        <v>BM24</v>
       </c>
       <c r="D1937" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F1937" s="1" t="s">
-        <v>274</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="1938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38619,17 +38703,11 @@
         <v>1265</v>
       </c>
       <c r="B1938" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C1938" s="88" t="str">
+        <v>25</v>
+      </c>
+      <c r="C1938" s="23" t="str">
         <f aca="false">CONCATENATE(A1938,B1938)</f>
-        <v>BM7</v>
-      </c>
-      <c r="D1938" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1938" s="1" t="s">
-        <v>274</v>
+        <v>BM25</v>
       </c>
     </row>
     <row r="1939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38637,965 +38715,695 @@
         <v>1265</v>
       </c>
       <c r="B1939" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C1939" s="88" t="str">
+        <v>26</v>
+      </c>
+      <c r="C1939" s="23" t="str">
         <f aca="false">CONCATENATE(A1939,B1939)</f>
-        <v>BM8</v>
+        <v>BM26</v>
       </c>
       <c r="D1939" s="1" t="n">
         <v>9</v>
       </c>
       <c r="F1939" s="1" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1940" s="7" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B1940" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="C1940" s="88" t="str">
-        <f aca="false">CONCATENATE(A1940,B1940)</f>
-        <v>BM9</v>
-      </c>
-      <c r="D1940" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1940" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C1940" s="23"/>
     </row>
     <row r="1941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1941" s="7" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B1941" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="C1941" s="88" t="str">
-        <f aca="false">CONCATENATE(A1941,B1941)</f>
-        <v>BM10</v>
-      </c>
-      <c r="D1941" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1941" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C1941" s="23"/>
     </row>
     <row r="1942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1942" s="7" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B1942" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="C1942" s="29" t="str">
-        <f aca="false">CONCATENATE(A1942,B1942)</f>
-        <v>BM11</v>
-      </c>
-      <c r="D1942" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1942" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C1942" s="23"/>
     </row>
     <row r="1943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1943" s="7" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B1943" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C1943" s="29" t="str">
-        <f aca="false">CONCATENATE(A1943,B1943)</f>
-        <v>BM12</v>
-      </c>
-      <c r="D1943" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1943" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C1943" s="23"/>
     </row>
     <row r="1944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1944" s="7" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B1944" s="8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C1944" s="23" t="str">
         <f aca="false">CONCATENATE(A1944,B1944)</f>
-        <v>BM13</v>
+        <v>BP1</v>
       </c>
     </row>
     <row r="1945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1945" s="7" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B1945" s="8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="C1945" s="23" t="str">
         <f aca="false">CONCATENATE(A1945,B1945)</f>
-        <v>BM14</v>
+        <v>BP2</v>
       </c>
     </row>
     <row r="1946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1946" s="7" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B1946" s="8" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C1946" s="23" t="str">
         <f aca="false">CONCATENATE(A1946,B1946)</f>
-        <v>BM15</v>
+        <v>BP3</v>
       </c>
     </row>
     <row r="1947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1947" s="7" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="B1947" s="8" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C1947" s="23" t="str">
         <f aca="false">CONCATENATE(A1947,B1947)</f>
-        <v>BM16</v>
+        <v>BP4</v>
       </c>
     </row>
     <row r="1948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1948" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1948" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="C1948" s="89" t="str">
+        <v>1</v>
+      </c>
+      <c r="C1948" s="23" t="str">
         <f aca="false">CONCATENATE(A1948,B1948)</f>
-        <v>BM17</v>
-      </c>
-      <c r="D1948" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1948" s="1" t="s">
-        <v>8</v>
+        <v>RAX1</v>
       </c>
     </row>
     <row r="1949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1949" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1949" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="C1949" s="89" t="str">
+        <v>2</v>
+      </c>
+      <c r="C1949" s="23" t="str">
         <f aca="false">CONCATENATE(A1949,B1949)</f>
-        <v>BM18</v>
-      </c>
-      <c r="D1949" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1949" s="1" t="s">
-        <v>13</v>
+        <v>RAX2</v>
       </c>
     </row>
     <row r="1950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1950" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1950" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C1950" s="89" t="str">
+        <v>3</v>
+      </c>
+      <c r="C1950" s="23" t="str">
         <f aca="false">CONCATENATE(A1950,B1950)</f>
-        <v>BM19</v>
-      </c>
-      <c r="D1950" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1950" s="1" t="s">
-        <v>170</v>
+        <v>RAX3</v>
       </c>
     </row>
     <row r="1951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1951" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1951" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C1951" s="89" t="str">
+        <v>4</v>
+      </c>
+      <c r="C1951" s="23" t="str">
         <f aca="false">CONCATENATE(A1951,B1951)</f>
-        <v>BM20</v>
-      </c>
-      <c r="D1951" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1951" s="1" t="s">
-        <v>8</v>
+        <v>RAX4</v>
       </c>
     </row>
     <row r="1952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1952" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1952" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C1952" s="89" t="str">
+        <v>5</v>
+      </c>
+      <c r="C1952" s="23" t="str">
         <f aca="false">CONCATENATE(A1952,B1952)</f>
-        <v>BM21</v>
-      </c>
-      <c r="D1952" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1952" s="1" t="s">
-        <v>274</v>
+        <v>RAX5</v>
       </c>
     </row>
     <row r="1953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1953" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1953" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C1953" s="89" t="str">
+        <v>6</v>
+      </c>
+      <c r="C1953" s="23" t="str">
         <f aca="false">CONCATENATE(A1953,B1953)</f>
-        <v>BM22</v>
-      </c>
-      <c r="D1953" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1953" s="1" t="s">
-        <v>183</v>
+        <v>RAX6</v>
       </c>
     </row>
     <row r="1954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1954" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1954" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C1954" s="89" t="str">
+        <v>7</v>
+      </c>
+      <c r="C1954" s="23" t="str">
         <f aca="false">CONCATENATE(A1954,B1954)</f>
-        <v>BM23</v>
-      </c>
-      <c r="D1954" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1954" s="1" t="s">
-        <v>99</v>
+        <v>RAX7</v>
       </c>
     </row>
     <row r="1955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1955" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1955" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C1955" s="89" t="str">
+        <v>8</v>
+      </c>
+      <c r="C1955" s="23" t="str">
         <f aca="false">CONCATENATE(A1955,B1955)</f>
-        <v>BM24</v>
-      </c>
-      <c r="D1955" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1955" s="1" t="s">
-        <v>1244</v>
+        <v>RAX8</v>
       </c>
     </row>
     <row r="1956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1956" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1956" s="8" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C1956" s="23" t="str">
         <f aca="false">CONCATENATE(A1956,B1956)</f>
-        <v>BM25</v>
+        <v>RAX9</v>
       </c>
     </row>
     <row r="1957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1957" s="7" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="B1957" s="8" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C1957" s="23" t="str">
         <f aca="false">CONCATENATE(A1957,B1957)</f>
-        <v>BM26</v>
-      </c>
-      <c r="D1957" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="F1957" s="1" t="s">
-        <v>8</v>
+        <v>RAX10</v>
       </c>
     </row>
     <row r="1958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1958" s="7" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="B1958" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1958" s="23"/>
+        <v>12</v>
+      </c>
+      <c r="C1958" s="23" t="str">
+        <f aca="false">CONCATENATE(A1958,B1958)</f>
+        <v>RAX12</v>
+      </c>
+      <c r="E1958" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1958" s="1" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="1959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1959" s="7" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="B1959" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C1959" s="23"/>
+        <v>13</v>
+      </c>
+      <c r="C1959" s="23" t="str">
+        <f aca="false">CONCATENATE(A1959,B1959)</f>
+        <v>RAX13</v>
+      </c>
     </row>
     <row r="1960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1960" s="7" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="B1960" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C1960" s="23"/>
+        <v>14</v>
+      </c>
+      <c r="C1960" s="23" t="str">
+        <f aca="false">CONCATENATE(A1960,B1960)</f>
+        <v>RAX14</v>
+      </c>
     </row>
     <row r="1961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1961" s="7" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="B1961" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C1961" s="23"/>
+        <v>15</v>
+      </c>
+      <c r="C1961" s="23" t="str">
+        <f aca="false">CONCATENATE(A1961,B1961)</f>
+        <v>RAX15</v>
+      </c>
     </row>
     <row r="1962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1962" s="7" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B1962" s="8" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C1962" s="23" t="str">
         <f aca="false">CONCATENATE(A1962,B1962)</f>
-        <v>BP1</v>
+        <v>RAX16</v>
       </c>
     </row>
     <row r="1963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1963" s="7" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="B1963" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1963" s="23" t="str">
         <f aca="false">CONCATENATE(A1963,B1963)</f>
-        <v>BP2</v>
+        <v>OSC1</v>
       </c>
     </row>
     <row r="1964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1964" s="7" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="B1964" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C1964" s="23" t="str">
         <f aca="false">CONCATENATE(A1964,B1964)</f>
-        <v>BP3</v>
+        <v>OSC2</v>
       </c>
     </row>
     <row r="1965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1965" s="7" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="B1965" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1965" s="23" t="str">
         <f aca="false">CONCATENATE(A1965,B1965)</f>
-        <v>BP4</v>
+        <v>OSC3</v>
       </c>
     </row>
     <row r="1966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1966" s="7" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B1966" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1966" s="23" t="str">
         <f aca="false">CONCATENATE(A1966,B1966)</f>
-        <v>RAX1</v>
+        <v>OSC4</v>
       </c>
     </row>
     <row r="1967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1967" s="7" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B1967" s="8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C1967" s="23" t="str">
         <f aca="false">CONCATENATE(A1967,B1967)</f>
-        <v>RAX2</v>
+        <v>OSC5</v>
       </c>
     </row>
     <row r="1968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1968" s="7" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B1968" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C1968" s="23" t="str">
         <f aca="false">CONCATENATE(A1968,B1968)</f>
-        <v>RAX3</v>
+        <v>OSC6</v>
       </c>
     </row>
     <row r="1969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1969" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1969" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C1969" s="23" t="str">
         <f aca="false">CONCATENATE(A1969,B1969)</f>
-        <v>RAX4</v>
+        <v>MUL1</v>
       </c>
     </row>
     <row r="1970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1970" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1970" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C1970" s="23" t="str">
         <f aca="false">CONCATENATE(A1970,B1970)</f>
-        <v>RAX5</v>
+        <v>MUL2</v>
       </c>
     </row>
     <row r="1971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1971" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1971" s="8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C1971" s="23" t="str">
         <f aca="false">CONCATENATE(A1971,B1971)</f>
-        <v>RAX6</v>
+        <v>MUL3</v>
       </c>
     </row>
     <row r="1972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1972" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1972" s="8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C1972" s="23" t="str">
         <f aca="false">CONCATENATE(A1972,B1972)</f>
-        <v>RAX7</v>
+        <v>MUL4</v>
       </c>
     </row>
     <row r="1973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1973" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1973" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C1973" s="23" t="str">
         <f aca="false">CONCATENATE(A1973,B1973)</f>
-        <v>RAX8</v>
+        <v>MUL5</v>
       </c>
     </row>
     <row r="1974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1974" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1974" s="8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1974" s="23" t="str">
         <f aca="false">CONCATENATE(A1974,B1974)</f>
-        <v>RAX9</v>
+        <v>MUL6</v>
       </c>
     </row>
     <row r="1975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1975" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1975" s="8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C1975" s="23" t="str">
         <f aca="false">CONCATENATE(A1975,B1975)</f>
-        <v>RAX10</v>
+        <v>MUL7</v>
       </c>
     </row>
     <row r="1976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1976" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1976" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C1976" s="23" t="str">
         <f aca="false">CONCATENATE(A1976,B1976)</f>
-        <v>RAX12</v>
-      </c>
-      <c r="E1976" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F1976" s="1" t="s">
-        <v>274</v>
+        <v>MUL8</v>
       </c>
     </row>
     <row r="1977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1977" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1977" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C1977" s="23" t="str">
         <f aca="false">CONCATENATE(A1977,B1977)</f>
-        <v>RAX13</v>
+        <v>MUL9</v>
       </c>
     </row>
     <row r="1978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1978" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1978" s="8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C1978" s="23" t="str">
         <f aca="false">CONCATENATE(A1978,B1978)</f>
-        <v>RAX14</v>
+        <v>MUL10</v>
       </c>
     </row>
     <row r="1979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1979" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1979" s="8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C1979" s="23" t="str">
         <f aca="false">CONCATENATE(A1979,B1979)</f>
-        <v>RAX15</v>
+        <v>MUL11</v>
       </c>
     </row>
     <row r="1980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1980" s="7" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B1980" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C1980" s="23" t="str">
         <f aca="false">CONCATENATE(A1980,B1980)</f>
-        <v>RAX16</v>
+        <v>MUL12</v>
       </c>
     </row>
     <row r="1981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1981" s="7" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B1981" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1981" s="23" t="str">
         <f aca="false">CONCATENATE(A1981,B1981)</f>
-        <v>OSC1</v>
+        <v>MUL13</v>
       </c>
     </row>
     <row r="1982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1982" s="7" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B1982" s="8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C1982" s="23" t="str">
         <f aca="false">CONCATENATE(A1982,B1982)</f>
-        <v>OSC2</v>
+        <v>MUL14</v>
       </c>
     </row>
     <row r="1983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1983" s="7" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B1983" s="8" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C1983" s="23" t="str">
         <f aca="false">CONCATENATE(A1983,B1983)</f>
-        <v>OSC3</v>
+        <v>MUL15</v>
       </c>
     </row>
     <row r="1984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1984" s="7" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B1984" s="8" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C1984" s="23" t="str">
         <f aca="false">CONCATENATE(A1984,B1984)</f>
-        <v>OSC4</v>
+        <v>MUL16</v>
       </c>
     </row>
     <row r="1985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1985" s="7" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B1985" s="8" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C1985" s="23" t="str">
         <f aca="false">CONCATENATE(A1985,B1985)</f>
-        <v>OSC5</v>
+        <v>MUL17</v>
       </c>
     </row>
     <row r="1986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1986" s="7" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B1986" s="8" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C1986" s="23" t="str">
         <f aca="false">CONCATENATE(A1986,B1986)</f>
-        <v>OSC6</v>
+        <v>MUL18</v>
       </c>
     </row>
     <row r="1987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1987" s="1" t="s">
+      <c r="A1987" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1987" s="2" t="n">
-        <v>1</v>
+      <c r="B1987" s="8" t="n">
+        <v>19</v>
       </c>
       <c r="C1987" s="23" t="str">
         <f aca="false">CONCATENATE(A1987,B1987)</f>
-        <v>MUL1</v>
+        <v>MUL19</v>
       </c>
     </row>
     <row r="1988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1988" s="1" t="s">
+      <c r="A1988" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1988" s="2" t="n">
-        <v>2</v>
+      <c r="B1988" s="8" t="n">
+        <v>20</v>
       </c>
       <c r="C1988" s="23" t="str">
         <f aca="false">CONCATENATE(A1988,B1988)</f>
-        <v>MUL2</v>
+        <v>MUL20</v>
       </c>
     </row>
     <row r="1989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1989" s="1" t="s">
+      <c r="A1989" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1989" s="2" t="n">
-        <v>3</v>
+      <c r="B1989" s="8" t="n">
+        <v>21</v>
       </c>
       <c r="C1989" s="23" t="str">
         <f aca="false">CONCATENATE(A1989,B1989)</f>
-        <v>MUL3</v>
+        <v>MUL21</v>
       </c>
     </row>
     <row r="1990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1990" s="1" t="s">
+      <c r="A1990" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1990" s="2" t="n">
-        <v>4</v>
+      <c r="B1990" s="8" t="n">
+        <v>22</v>
       </c>
       <c r="C1990" s="23" t="str">
         <f aca="false">CONCATENATE(A1990,B1990)</f>
-        <v>MUL4</v>
+        <v>MUL22</v>
       </c>
     </row>
     <row r="1991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1991" s="1" t="s">
+      <c r="A1991" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1991" s="2" t="n">
-        <v>5</v>
+      <c r="B1991" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="C1991" s="23" t="str">
         <f aca="false">CONCATENATE(A1991,B1991)</f>
-        <v>MUL5</v>
+        <v>MUL23</v>
       </c>
     </row>
     <row r="1992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1992" s="1" t="s">
+      <c r="A1992" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1992" s="2" t="n">
-        <v>6</v>
+      <c r="B1992" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="C1992" s="23" t="str">
         <f aca="false">CONCATENATE(A1992,B1992)</f>
-        <v>MUL6</v>
+        <v>MUL24</v>
       </c>
     </row>
     <row r="1993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1993" s="1" t="s">
+      <c r="A1993" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1993" s="2" t="n">
-        <v>7</v>
+      <c r="B1993" s="8" t="n">
+        <v>25</v>
       </c>
       <c r="C1993" s="23" t="str">
         <f aca="false">CONCATENATE(A1993,B1993)</f>
-        <v>MUL7</v>
+        <v>MUL25</v>
       </c>
     </row>
     <row r="1994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1994" s="1" t="s">
+      <c r="A1994" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1994" s="2" t="n">
-        <v>8</v>
+      <c r="B1994" s="8" t="n">
+        <v>26</v>
       </c>
       <c r="C1994" s="23" t="str">
         <f aca="false">CONCATENATE(A1994,B1994)</f>
-        <v>MUL8</v>
+        <v>MUL26</v>
       </c>
     </row>
     <row r="1995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1995" s="1" t="s">
+      <c r="A1995" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1995" s="2" t="n">
-        <v>9</v>
+      <c r="B1995" s="8" t="n">
+        <v>27</v>
       </c>
       <c r="C1995" s="23" t="str">
         <f aca="false">CONCATENATE(A1995,B1995)</f>
-        <v>MUL9</v>
+        <v>MUL27</v>
       </c>
     </row>
     <row r="1996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1996" s="1" t="s">
+      <c r="A1996" s="7" t="s">
         <v>1270</v>
       </c>
-      <c r="B1996" s="2" t="n">
-        <v>10</v>
+      <c r="B1996" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="C1996" s="23" t="str">
         <f aca="false">CONCATENATE(A1996,B1996)</f>
-        <v>MUL10</v>
-      </c>
-    </row>
-    <row r="1997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1997" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B1997" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C1997" s="23" t="str">
-        <f aca="false">CONCATENATE(A1997,B1997)</f>
-        <v>MUL11</v>
-      </c>
-    </row>
-    <row r="1998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1998" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B1998" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C1998" s="23" t="str">
-        <f aca="false">CONCATENATE(A1998,B1998)</f>
-        <v>MUL12</v>
-      </c>
-    </row>
-    <row r="1999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1999" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B1999" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="C1999" s="23" t="str">
-        <f aca="false">CONCATENATE(A1999,B1999)</f>
-        <v>MUL13</v>
-      </c>
-    </row>
-    <row r="2000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2000" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2000" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C2000" s="23" t="str">
-        <f aca="false">CONCATENATE(A2000,B2000)</f>
-        <v>MUL14</v>
-      </c>
-    </row>
-    <row r="2001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2001" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2001" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="C2001" s="23" t="str">
-        <f aca="false">CONCATENATE(A2001,B2001)</f>
-        <v>MUL15</v>
-      </c>
-    </row>
-    <row r="2002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2002" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2002" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="C2002" s="23" t="str">
-        <f aca="false">CONCATENATE(A2002,B2002)</f>
-        <v>MUL16</v>
-      </c>
-    </row>
-    <row r="2003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2003" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2003" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="C2003" s="23" t="str">
-        <f aca="false">CONCATENATE(A2003,B2003)</f>
-        <v>MUL17</v>
-      </c>
-    </row>
-    <row r="2004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2004" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2004" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="C2004" s="23" t="str">
-        <f aca="false">CONCATENATE(A2004,B2004)</f>
-        <v>MUL18</v>
-      </c>
-    </row>
-    <row r="2005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2005" s="7" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2005" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C2005" s="23" t="str">
-        <f aca="false">CONCATENATE(A2005,B2005)</f>
-        <v>MUL19</v>
-      </c>
-    </row>
-    <row r="2006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2006" s="7" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2006" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C2006" s="23" t="str">
-        <f aca="false">CONCATENATE(A2006,B2006)</f>
-        <v>MUL20</v>
-      </c>
-    </row>
-    <row r="2007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2007" s="7" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2007" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="C2007" s="23" t="str">
-        <f aca="false">CONCATENATE(A2007,B2007)</f>
-        <v>MUL21</v>
-      </c>
-    </row>
-    <row r="2008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2008" s="7" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2008" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="C2008" s="23" t="str">
-        <f aca="false">CONCATENATE(A2008,B2008)</f>
-        <v>MUL22</v>
-      </c>
-    </row>
-    <row r="2009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2009" s="7" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2009" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="C2009" s="23" t="str">
-        <f aca="false">CONCATENATE(A2009,B2009)</f>
-        <v>MUL23</v>
-      </c>
-    </row>
-    <row r="2010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2010" s="7" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2010" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="C2010" s="23" t="str">
-        <f aca="false">CONCATENATE(A2010,B2010)</f>
-        <v>MUL24</v>
-      </c>
-    </row>
-    <row r="2011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2011" s="7" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2011" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="C2011" s="23" t="str">
-        <f aca="false">CONCATENATE(A2011,B2011)</f>
-        <v>MUL25</v>
-      </c>
-    </row>
-    <row r="2012" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2012" s="7" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B2012" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="C2012" s="23" t="str">
-        <f aca="false">CONCATENATE(A2012,B2012)</f>
-        <v>MUL26</v>
+        <v>MUL28</v>
       </c>
     </row>
   </sheetData>
